--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,412 +656,424 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>506400</v>
+      </c>
+      <c r="E8" s="3">
         <v>532400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>525300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>562400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>468900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>499200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>509600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>527700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>477900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>518000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>549500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>534200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>496700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>485400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>260000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>469700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>401800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>431900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>429500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>461200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>355900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>387400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>385500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>408000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>321800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>346100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>337500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>369900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>277100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E9" s="3">
         <v>252000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>247800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>254100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>222200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>232800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>234600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>236000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>217700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>226500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>235900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>224700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>216500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>210800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>140800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>218600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>187500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>204500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>202500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>212000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>173500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>182600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>177100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>180500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>152400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>162400</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>130300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>259400</v>
+      </c>
+      <c r="E10" s="3">
         <v>280400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>277500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>308300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>246700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>266400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>275000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>291700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>260200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>291500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>313600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>309500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>280200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>274600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>119200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>251100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>214300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>227400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>227000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>249200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>182400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>204800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>208400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>227500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>169400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>183700</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>146800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1094,8 +1106,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1186,8 +1199,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1278,192 +1294,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>80800</v>
+        <v>5400</v>
       </c>
       <c r="E14" s="3">
+        <v>83100</v>
+      </c>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>13300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>3100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>8000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>7100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E15" s="3">
         <v>24400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>25200</v>
       </c>
       <c r="J15" s="3">
         <v>25200</v>
       </c>
       <c r="K15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="L15" s="3">
         <v>24500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>24800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>23700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>22300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>20800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>20400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>19300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>17600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>17900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>17600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>15400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>14600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>14400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>13800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1493,192 +1518,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>520300</v>
+      </c>
+      <c r="E17" s="3">
         <v>607000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>517600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>529100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>478700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>483800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>491200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>490400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>469900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>467300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>494700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>472700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>439800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>430600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>301600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>452800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>393400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>430600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>407700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>428800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>377800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>389500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>360600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>369100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>327600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>329500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>280500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-74600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>61500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>56900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>54800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-41600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>38900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1711,44 +1743,45 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1791,117 +1824,123 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-50400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>34400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>56800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>43300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>70300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>70700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>69500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>85000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>79500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>77000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>23700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>52800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>56700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>31900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>10400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="E22" s="3">
         <v>3500</v>
@@ -1910,269 +1949,278 @@
         <v>3500</v>
       </c>
       <c r="G22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H22" s="3">
         <v>3600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3700</v>
       </c>
       <c r="I22" s="3">
         <v>3700</v>
       </c>
       <c r="J22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K22" s="3">
         <v>3600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>700</v>
       </c>
       <c r="L22" s="3">
         <v>700</v>
       </c>
       <c r="M22" s="3">
+        <v>700</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9300</v>
-      </c>
-      <c r="X22" s="3">
-        <v>9400</v>
       </c>
       <c r="Y22" s="3">
         <v>9400</v>
       </c>
       <c r="Z22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>9300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9700</v>
       </c>
       <c r="AF22" s="3">
         <v>9700</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-78300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>44600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>55100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>44100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-57200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>23300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>29500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>25500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-13400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-10900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2263,192 +2311,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-73800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>43400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-43800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>24500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-73800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>41000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>43400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-43800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>17400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>24500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2539,8 +2596,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2595,8 +2655,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2613,12 +2673,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>42100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2631,8 +2691,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2723,8 +2786,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2815,44 +2881,47 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2895,112 +2964,118 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-73800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-43800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>17400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>24500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3091,197 +3166,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-73800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-43800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>17400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>24500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3314,8 +3398,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3348,100 +3433,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E41" s="3">
         <v>265800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>254600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>246900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>229400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>256200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>254400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>314600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>305800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>439100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>408300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>453800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>373900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>377000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>256300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>263200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>94100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>82800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>34600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>58400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24900</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3532,183 +3621,189 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E43" s="3">
         <v>76600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>78900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>63800</v>
       </c>
       <c r="I43" s="3">
         <v>63800</v>
       </c>
       <c r="J43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K43" s="3">
         <v>62200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>55700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>58000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>38900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>45100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>41700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>43200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>39100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>38200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E44" s="3">
         <v>120600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>120900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>123500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>123200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>122000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>129500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>127400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>123700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>124600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>119500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>111300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>111700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>117900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>130400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>127600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>111900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>105700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>111900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>116000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>99300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>94900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>93700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>89400</v>
       </c>
       <c r="AC44" s="3">
         <v>89400</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
+      <c r="AD44" s="3">
+        <v>89400</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>5</v>
@@ -3716,192 +3811,201 @@
       <c r="AF44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E45" s="3">
         <v>37000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>25000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>30800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24100</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>24800</v>
       </c>
       <c r="Z45" s="3">
         <v>24800</v>
       </c>
       <c r="AA45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AB45" s="3">
         <v>23900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>396700</v>
+      </c>
+      <c r="E46" s="3">
         <v>500100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>494300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>486500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>473800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>477100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>480500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>532600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>514600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>646400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>608400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>657000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>566700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>555400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>453100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>441200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>234600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>278600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>270900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>270100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>214700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>211100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>199400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>218600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>162500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>178800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>174400</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3911,8 +4015,8 @@
       <c r="E47" s="3">
         <v>900</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
+      <c r="F47" s="3">
+        <v>900</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
@@ -3929,8 +4033,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3992,192 +4096,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>769100</v>
+      </c>
+      <c r="E48" s="3">
         <v>760800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>765800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>751600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>742600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>738300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>723000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>712300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>701300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>678200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>679200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>679800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>681400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>666200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>681600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>693500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>714900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>716200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>715900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>695300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>355100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>340600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>328000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>311000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>302300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>290700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>281300</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>978400</v>
+      </c>
+      <c r="E49" s="3">
         <v>978900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1049100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1050900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1052800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1054600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1056400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1058300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1060200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1062100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1063900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1065800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1067700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1069500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1071400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1073200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1075100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1077000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1078800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1080600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1082700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1099900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4268,8 +4381,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4360,100 +4476,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E52" s="3">
         <v>25800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10500</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4544,100 +4666,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2172500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2266400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2333900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2312400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2291200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2291700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2278300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2325500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2293100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2405500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2369200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2419800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2333500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2307500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2219000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2218700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2032700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2078400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2071800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2053100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1661400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1660700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1639400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4670,8 +4798,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4704,183 +4833,187 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E57" s="3">
         <v>62900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>64100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>74600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>65300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>70000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>69400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>76100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>77700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>79800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>68600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>52400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>60000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>43600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>30900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>46100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>35700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>33600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34400</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4700</v>
       </c>
       <c r="J58" s="3">
         <v>4700</v>
       </c>
       <c r="K58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L58" s="3">
         <v>4000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13700</v>
-      </c>
-      <c r="U58" s="3">
-        <v>8500</v>
       </c>
       <c r="V58" s="3">
         <v>8500</v>
       </c>
       <c r="W58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="X58" s="3">
         <v>7600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7700</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>7300</v>
       </c>
       <c r="AA58" s="3">
         <v>7300</v>
       </c>
       <c r="AB58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AC58" s="3">
         <v>9600</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
+      <c r="AD58" s="3">
+        <v>9600</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
@@ -4888,376 +5021,391 @@
       <c r="AF58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>319700</v>
+      </c>
+      <c r="E59" s="3">
         <v>300000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>288600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>283900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>274900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>263700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>279100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>271300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>275500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>268300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>288500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>275900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>260200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>283900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>256200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>224000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>218600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>244800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>232700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>244100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>160400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>158500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>148800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>168200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>169500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>176000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>167900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>397700</v>
+      </c>
+      <c r="E60" s="3">
         <v>373500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>363200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>361800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>344300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>336600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>353800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>345400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>343800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>348800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>370500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>359800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>328700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>356000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>311900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>287500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>273200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>303900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>288300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>297700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>211700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>197200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>189300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>221700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>211300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>219200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>211900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>450800</v>
+      </c>
+      <c r="E61" s="3">
         <v>552200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>555200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>563700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>563400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>564200</v>
       </c>
       <c r="I61" s="3">
         <v>564200</v>
       </c>
       <c r="J61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="K61" s="3">
         <v>564700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>566100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>615600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>616200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>733700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>651800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>648100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>644900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>713200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>555900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>584300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>579100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>578400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>570500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>566900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>566600</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>562000</v>
       </c>
       <c r="AA61" s="3">
         <v>562000</v>
       </c>
       <c r="AB61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>912700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>913300</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>494600</v>
+      </c>
+      <c r="E62" s="3">
         <v>500400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>507100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>490200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>482500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>484000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>468700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>464700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>457200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>452500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>444200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>438800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>446600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>438400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>441200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>431900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>427200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>424800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>430000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>414400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>136000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>138400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>154000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>149600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>154100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>202400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>202000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5348,8 +5496,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5440,8 +5591,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5532,100 +5686,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1343100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1426100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1425500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1415600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1390100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1384800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1386700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1374800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1367100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1416900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1430900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1532300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1427000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1442600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1398100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1432600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1256300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1313000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1297400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1290500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>918200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>902500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>909900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>933300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>927300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5658,8 +5818,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5750,8 +5911,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5842,8 +6006,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5934,8 +6101,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6026,100 +6196,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>254600</v>
+      </c>
+      <c r="E72" s="3">
         <v>270600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>344400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>338800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>320500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>329800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>318300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>308500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>278400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>272200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>231200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>193600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>142900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>107800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>72500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>116300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>107100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>103200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>102000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>91800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>74800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>100100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>94300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>81200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>32200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6900</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6210,8 +6386,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6302,8 +6481,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6394,100 +6576,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>829400</v>
+      </c>
+      <c r="E76" s="3">
         <v>840400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>908400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>896700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>901100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>906900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>891700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>950700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>926000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>988600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>938300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>887500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>906500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>865000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>820900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>786200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>776400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>765500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>774400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>762600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>743200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>758200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>729600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>711300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>654600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>254600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>249500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6578,197 +6766,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-73800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-43800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>17400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>24500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6801,100 +6998,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E83" s="3">
         <v>24400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>25200</v>
       </c>
       <c r="J83" s="3">
         <v>25200</v>
       </c>
       <c r="K83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="L83" s="3">
         <v>24500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>22600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>23700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>14600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>14400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6985,8 +7186,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7077,8 +7281,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7169,8 +7376,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7261,8 +7471,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7353,100 +7566,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E89" s="3">
         <v>41100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>47100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>92200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>97700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>132300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>86100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>36300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>83000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>77800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>28300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>21400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>46500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7479,100 +7698,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-24900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7663,8 +7886,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7755,100 +7981,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-25500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-30100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7881,8 +8113,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7965,16 +8198,19 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8065,8 +8301,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8157,8 +8396,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8249,100 +8491,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-102600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-73700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-122300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-115400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>20800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>150600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8433,96 +8681,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-116100</v>
+      </c>
+      <c r="E102" s="3">
         <v>11200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-60400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-133600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>80200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>120800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>223800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-55000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>55900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-32100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>54800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>25400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,424 +656,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E8" s="3">
         <v>506400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>532400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>525300</v>
       </c>
-      <c r="G8" s="3">
-        <v>562400</v>
-      </c>
       <c r="H8" s="3">
+        <v>520800</v>
+      </c>
+      <c r="I8" s="3">
         <v>468900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>499200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>509600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>527700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>477900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>518000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>549500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>534200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>496700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>485400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>260000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>469700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>401800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>431900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>429500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>461200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>355900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>387400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>385500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>408000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>321800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>346100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>337500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>369900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>277100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>248700</v>
+      </c>
+      <c r="E9" s="3">
         <v>247000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>252000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>247800</v>
       </c>
-      <c r="G9" s="3">
-        <v>254100</v>
-      </c>
       <c r="H9" s="3">
+        <v>235400</v>
+      </c>
+      <c r="I9" s="3">
         <v>222200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>232800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>234600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>236000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>217700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>226500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>235900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>224700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>216500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>210800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>140800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>218600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>187500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>204500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>202500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>212000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>173500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>182600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>177100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>180500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>152400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>162400</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>130300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E10" s="3">
         <v>259400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>280400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>277500</v>
       </c>
-      <c r="G10" s="3">
-        <v>308300</v>
-      </c>
       <c r="H10" s="3">
+        <v>285400</v>
+      </c>
+      <c r="I10" s="3">
         <v>246700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>266400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>275000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>291700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>260200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>291500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>313600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>309500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>280200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>274600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>119200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>251100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>214300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>227400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>227000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>249200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>182400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>204800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>208400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>227500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>169400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>183700</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>146800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1120,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1202,8 +1216,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1297,198 +1314,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E14" s="3">
         <v>5400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>83100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>13300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>8000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>7100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E15" s="3">
         <v>24100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24900</v>
       </c>
-      <c r="G15" s="3">
-        <v>24800</v>
-      </c>
       <c r="H15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I15" s="3">
         <v>24700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>25200</v>
       </c>
       <c r="K15" s="3">
         <v>25200</v>
       </c>
       <c r="L15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="M15" s="3">
         <v>24500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>21900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>24800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>20800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>19300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>17600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>17900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>15400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>14600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>14400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1519,198 +1545,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>518100</v>
+      </c>
+      <c r="E17" s="3">
         <v>520300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>607000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>517600</v>
       </c>
-      <c r="G17" s="3">
-        <v>529100</v>
-      </c>
       <c r="H17" s="3">
+        <v>491700</v>
+      </c>
+      <c r="I17" s="3">
         <v>478700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>483800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>491200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>490400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>469900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>467300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>494700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>472700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>439800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>430600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>301600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>452800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>393400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>430600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>407700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>428800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>377800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>389500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>360600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>369100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>327600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>329500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>280500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-74600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7700</v>
       </c>
-      <c r="G18" s="3">
-        <v>33300</v>
-      </c>
       <c r="H18" s="3">
+        <v>29100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>61500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>56900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-41600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>38900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1744,47 +1777,48 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1827,123 +1861,129 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
+      <c r="AD20" s="3">
+        <v>0</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E21" s="3">
         <v>12600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-50400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>34400</v>
       </c>
-      <c r="G21" s="3">
-        <v>56800</v>
-      </c>
       <c r="H21" s="3">
+        <v>52500</v>
+      </c>
+      <c r="I21" s="3">
         <v>15900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>70300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>70700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>69500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>85000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>79500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>77000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-19700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>32000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>23700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>52800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>56700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>31900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>10400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>3100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3500</v>
       </c>
       <c r="F22" s="3">
         <v>3500</v>
@@ -1952,275 +1992,284 @@
         <v>3500</v>
       </c>
       <c r="H22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I22" s="3">
         <v>3600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3700</v>
       </c>
       <c r="J22" s="3">
         <v>3700</v>
       </c>
       <c r="K22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L22" s="3">
         <v>3600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>9400</v>
       </c>
       <c r="Z22" s="3">
         <v>9400</v>
       </c>
       <c r="AA22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>9300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>9700</v>
       </c>
       <c r="AG22" s="3">
         <v>9700</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5900</v>
       </c>
-      <c r="G23" s="3">
-        <v>28400</v>
-      </c>
       <c r="H23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-12400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>44600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>55100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-57200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>23300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>15500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>29500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>25500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
-        <v>10200</v>
-      </c>
       <c r="H24" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I24" s="3">
         <v>-3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-13400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-16700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2314,198 +2363,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-73800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5600</v>
       </c>
-      <c r="G26" s="3">
-        <v>18300</v>
-      </c>
       <c r="H26" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-9300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-43800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>24500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-73800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
-        <v>18300</v>
-      </c>
       <c r="H27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-9300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>43400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-43800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>17400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>24500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2599,31 +2657,34 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-600</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>2300</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2658,8 +2719,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2676,12 +2737,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>42100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2694,8 +2755,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2789,8 +2853,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2884,47 +2951,50 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2967,115 +3037,121 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
+      <c r="AD32" s="3">
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>43400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-43800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>17400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3169,203 +3245,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>43400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-43800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>17400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3399,8 +3484,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3434,103 +3520,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>150100</v>
+      </c>
+      <c r="E41" s="3">
         <v>149900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>265800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>254600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>246900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>229400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>256200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>254400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>314600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>305800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>439100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>408300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>453800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>373900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>377000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>256300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>263200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>94100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>82800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>17100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>48900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>34600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>58400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24900</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3624,189 +3714,195 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E43" s="3">
         <v>86900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>76600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>78900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>79900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>63800</v>
       </c>
       <c r="J43" s="3">
         <v>63800</v>
       </c>
       <c r="K43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="L43" s="3">
         <v>62200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>55700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>58000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>38900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>45100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>41700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>43200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>39100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>38200</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E44" s="3">
         <v>119900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>120600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>120900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>123500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>123200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>129500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>127400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>123700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>124600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>120900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>119500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>111300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>111700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>117900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>130400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>127600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>111900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>105700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>111900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>116000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>99300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>94900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>93700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>89400</v>
       </c>
       <c r="AD44" s="3">
         <v>89400</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
+      <c r="AE44" s="3">
+        <v>89400</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>5</v>
@@ -3814,203 +3910,212 @@
       <c r="AG44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E45" s="3">
         <v>40000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>30800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24100</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>24800</v>
       </c>
       <c r="AA45" s="3">
         <v>24800</v>
       </c>
       <c r="AB45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AC45" s="3">
         <v>23900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>22000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>378900</v>
+      </c>
+      <c r="E46" s="3">
         <v>396700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>494300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>486500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>473800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>477100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>480500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>532600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>514600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>646400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>608400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>657000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>566700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>555400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>453100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>441200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>234600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>278600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>270900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>270100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>214700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>211100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>199400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>218600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>162500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>178800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>174400</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>900</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
         <v>900</v>
@@ -4018,8 +4123,8 @@
       <c r="F47" s="3">
         <v>900</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
+      <c r="G47" s="3">
+        <v>900</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
@@ -4036,8 +4141,8 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4099,198 +4204,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>768100</v>
+      </c>
+      <c r="E48" s="3">
         <v>769100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>760800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>765800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>751600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>742600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>738300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>723000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>712300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>701300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>678200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>679200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>679800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>681400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>666200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>681600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>693500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>714900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>716200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>715900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>695300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>355100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>340600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>328000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>311000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>302300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>290700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>281300</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>977900</v>
+      </c>
+      <c r="E49" s="3">
         <v>978400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>978900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1049100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1050900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1052800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1054600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1056400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1058300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1060200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1062100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1063900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1065800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1067700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1069500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1071400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1073200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1075100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1077000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1078800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1080600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1082700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1099900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4384,8 +4498,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4479,103 +4596,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E52" s="3">
         <v>27400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10500</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4669,103 +4792,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2155400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2172500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2266400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2333900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2312400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2291200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2291700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2278300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2325500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2293100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2405500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2369200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2419800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2333500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2307500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2219000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2218700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2032700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2078400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2071800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2053100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1661400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1660700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4799,8 +4928,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4834,189 +4964,193 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E57" s="3">
         <v>67600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>64100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>74600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>65300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>69000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>70000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>64300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>76100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>77700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>79800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>68600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>52400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>60000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>47100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>45100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>43600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>30900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>46100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>35700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>33600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>34400</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E58" s="3">
         <v>10500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>4700</v>
       </c>
       <c r="K58" s="3">
         <v>4700</v>
       </c>
       <c r="L58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13700</v>
-      </c>
-      <c r="V58" s="3">
-        <v>8500</v>
       </c>
       <c r="W58" s="3">
         <v>8500</v>
       </c>
       <c r="X58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="Y58" s="3">
         <v>7600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>7300</v>
       </c>
       <c r="AB58" s="3">
         <v>7300</v>
       </c>
       <c r="AC58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AD58" s="3">
         <v>9600</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
+      <c r="AE58" s="3">
+        <v>9600</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>5</v>
@@ -5024,388 +5158,403 @@
       <c r="AG58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E59" s="3">
         <v>319700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>288600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>283900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>274900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>263700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>279100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>271300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>275500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>268300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>288500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>275900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>260200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>283900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>256200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>224000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>218600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>244800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>232700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>244100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>160400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>158500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>148800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>168200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>169500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>176000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>167900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E60" s="3">
         <v>397700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>373500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>363200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>361800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>344300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>336600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>353800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>345400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>343800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>348800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>370500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>359800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>328700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>356000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>311900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>287500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>273200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>303900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>288300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>297700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>211700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>197200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>189300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>221700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>211300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>219200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>448600</v>
+      </c>
+      <c r="E61" s="3">
         <v>450800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>552200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>555200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>563700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>563400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>564200</v>
       </c>
       <c r="J61" s="3">
         <v>564200</v>
       </c>
       <c r="K61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="L61" s="3">
         <v>564700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>566100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>615600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>616200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>733700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>651800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>648100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>644900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>713200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>555900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>584300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>579100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>578400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>570500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>566900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>562000</v>
       </c>
       <c r="AB61" s="3">
         <v>562000</v>
       </c>
       <c r="AC61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>912700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>913300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>490400</v>
+      </c>
+      <c r="E62" s="3">
         <v>494600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>507100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>490200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>482500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>484000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>468700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>464700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>457200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>452500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>444200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>438800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>446600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>438400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>441200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>431900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>427200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>424800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>430000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>414400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>136000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>138400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>154000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>149600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>154100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>202400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>202000</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5499,8 +5648,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5594,8 +5746,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5689,103 +5844,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1314000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1343100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1426100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1425500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1415600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1390100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1384800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1386700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1374800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1367100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1416900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1430900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1532300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1427000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1442600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1398100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1432600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1256300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1313000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1297400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1290500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>918200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>902500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>909900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>933300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>927300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5819,8 +5980,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5914,8 +6076,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6009,8 +6174,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6104,8 +6272,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6199,103 +6370,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E72" s="3">
         <v>254600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>270600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>344400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>338800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>320500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>329800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>318300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>308500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>278400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>272200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>231200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>193600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>142900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>107800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>72500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>116300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>107100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>103200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>102000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>91800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>74800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>100100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>94300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>81200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>32200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6389,8 +6566,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6484,8 +6664,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6579,103 +6762,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>841300</v>
+      </c>
+      <c r="E76" s="3">
         <v>829400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>840400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>908400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>896700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>901100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>906900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>891700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>950700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>926000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>988600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>938300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>887500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>906500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>865000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>820900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>786200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>776400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>765500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>774400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>762600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>743200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>758200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>729600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>711300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>654600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>254600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>249500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6769,203 +6958,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>43400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-43800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>17400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6999,103 +7197,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E83" s="3">
         <v>27300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>25200</v>
       </c>
       <c r="K83" s="3">
         <v>25200</v>
       </c>
       <c r="L83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="M83" s="3">
         <v>24500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>21900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>23700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>14600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7189,8 +7391,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7284,8 +7489,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7379,8 +7587,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7474,8 +7685,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7569,103 +7783,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E89" s="3">
         <v>19800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>92200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>97700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>132300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>86100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>36300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>83000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>77800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>28300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>21400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>46500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7699,103 +7919,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7889,8 +8113,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7984,103 +8211,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-24100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-26000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-25800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8114,8 +8347,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8201,16 +8435,19 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8304,8 +8541,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8399,8 +8639,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8494,103 +8737,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-102600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-73700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-122300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-115400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>20800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>150600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8684,99 +8933,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-116100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-60400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-133600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>80200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>120800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>223800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-55000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>55900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>54800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>25400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -656,437 +656,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>542500</v>
+        <v>451700</v>
       </c>
       <c r="E8" s="3">
+        <v>482800</v>
+      </c>
+      <c r="F8" s="3">
         <v>506400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>532400</v>
       </c>
-      <c r="G8" s="3">
-        <v>525300</v>
-      </c>
       <c r="H8" s="3">
-        <v>520800</v>
+        <v>431800</v>
       </c>
       <c r="I8" s="3">
+        <v>464800</v>
+      </c>
+      <c r="J8" s="3">
         <v>468900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>499200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>509600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>527700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>477900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>518000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>549500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>534200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>496700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>485400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>260000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>469700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>401800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>431900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>429500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>461200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>355900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>387400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>385500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>408000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>321800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>346100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>337500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>369900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>277100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>248700</v>
+        <v>193600</v>
       </c>
       <c r="E9" s="3">
+        <v>195500</v>
+      </c>
+      <c r="F9" s="3">
         <v>247000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>252000</v>
       </c>
-      <c r="G9" s="3">
-        <v>247800</v>
-      </c>
       <c r="H9" s="3">
-        <v>235400</v>
+        <v>180300</v>
       </c>
       <c r="I9" s="3">
+        <v>186100</v>
+      </c>
+      <c r="J9" s="3">
         <v>222200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>232800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>234600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>236000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>217700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>226500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>235900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>224700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>216500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>210800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>140800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>218600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>187500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>204500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>202500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>212000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>173500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>182600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>177100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>180500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>152400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>162400</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>130300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>293800</v>
+        <v>258100</v>
       </c>
       <c r="E10" s="3">
+        <v>287300</v>
+      </c>
+      <c r="F10" s="3">
         <v>259400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>280400</v>
       </c>
-      <c r="G10" s="3">
-        <v>277500</v>
-      </c>
       <c r="H10" s="3">
-        <v>285400</v>
+        <v>251500</v>
       </c>
       <c r="I10" s="3">
+        <v>278700</v>
+      </c>
+      <c r="J10" s="3">
         <v>246700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>266400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>275000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>291700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>260200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>291500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>313600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>309500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>280200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>274600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>119200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>251100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>214300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>227400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>227000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>249200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>182400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>204800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>208400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>227500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>169400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>183700</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>146800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1121,8 +1134,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1219,8 +1233,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1317,204 +1334,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E14" s="3">
         <v>5600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>83100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>15800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>13300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>3100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>8000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>7100</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E15" s="3">
         <v>23600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>24700</v>
+      </c>
+      <c r="K15" s="3">
         <v>24900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>22700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>24700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>24900</v>
-      </c>
-      <c r="K15" s="3">
-        <v>25200</v>
       </c>
       <c r="L15" s="3">
         <v>25200</v>
       </c>
       <c r="M15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="N15" s="3">
         <v>24500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>21900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>24800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>23700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>22300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>20300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>19300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>17600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>17600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>15400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>14600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>14400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>13800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1546,204 +1572,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>518100</v>
+        <v>451100</v>
       </c>
       <c r="E17" s="3">
+        <v>459400</v>
+      </c>
+      <c r="F17" s="3">
         <v>520300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>607000</v>
       </c>
-      <c r="G17" s="3">
-        <v>517600</v>
-      </c>
       <c r="H17" s="3">
-        <v>491700</v>
+        <v>426200</v>
       </c>
       <c r="I17" s="3">
+        <v>437000</v>
+      </c>
+      <c r="J17" s="3">
         <v>478700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>483800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>491200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>490400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>469900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>467300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>494700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>472700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>439800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>430600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>301600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>452800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>393400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>430600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>407700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>428800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>377800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>389500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>360600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>369100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>327600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>329500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>280500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>24400</v>
+        <v>600</v>
       </c>
       <c r="E18" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-74600</v>
       </c>
-      <c r="G18" s="3">
-        <v>7700</v>
-      </c>
       <c r="H18" s="3">
-        <v>29100</v>
+        <v>5600</v>
       </c>
       <c r="I18" s="3">
+        <v>27800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>54800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>61500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>56900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>54800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>38900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16600</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1778,50 +1811,51 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1864,118 +1898,124 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
+      <c r="AE20" s="3">
+        <v>0</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>48100</v>
+        <v>23100</v>
       </c>
       <c r="E21" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F21" s="3">
         <v>12600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-50400</v>
       </c>
-      <c r="G21" s="3">
-        <v>34400</v>
-      </c>
       <c r="H21" s="3">
-        <v>52500</v>
+        <v>32200</v>
       </c>
       <c r="I21" s="3">
+        <v>51200</v>
+      </c>
+      <c r="J21" s="3">
         <v>15900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>45900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>70300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>70700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>69500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>85000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>79500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>77000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-19700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>32000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>23700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>52800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>17300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>56700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>31900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>10400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1983,10 +2023,10 @@
         <v>2700</v>
       </c>
       <c r="E22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F22" s="3">
         <v>3100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3500</v>
       </c>
       <c r="G22" s="3">
         <v>3500</v>
@@ -1995,281 +2035,290 @@
         <v>3500</v>
       </c>
       <c r="I22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J22" s="3">
         <v>3600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3700</v>
       </c>
       <c r="K22" s="3">
         <v>3700</v>
       </c>
       <c r="L22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M22" s="3">
         <v>3600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>9400</v>
       </c>
       <c r="AA22" s="3">
         <v>9400</v>
       </c>
       <c r="AB22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>9300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>9700</v>
       </c>
       <c r="AH22" s="3">
         <v>9700</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>20200</v>
+        <v>-2600</v>
       </c>
       <c r="E23" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-78300</v>
       </c>
-      <c r="G23" s="3">
-        <v>5900</v>
-      </c>
       <c r="H23" s="3">
-        <v>24200</v>
+        <v>3700</v>
       </c>
       <c r="I23" s="3">
+        <v>22900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-12400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>44600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>55100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>42300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-57200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>29500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>25500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>7900</v>
       </c>
-      <c r="E24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>8200</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-13400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2366,204 +2415,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>12200</v>
+        <v>-1000</v>
       </c>
       <c r="E26" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-16000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73800</v>
       </c>
-      <c r="G26" s="3">
-        <v>5600</v>
-      </c>
       <c r="H26" s="3">
-        <v>16000</v>
+        <v>3600</v>
       </c>
       <c r="I26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>41000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>43400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>24500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1500</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12200</v>
+        <v>-1000</v>
       </c>
       <c r="E27" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-16000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73800</v>
       </c>
-      <c r="G27" s="3">
-        <v>5600</v>
-      </c>
       <c r="H27" s="3">
-        <v>16000</v>
+        <v>3600</v>
       </c>
       <c r="I27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>41000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>43400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-43800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>24500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2660,16 +2718,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-600</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+        <v>-2100</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-100</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>5</v>
@@ -2678,16 +2739,16 @@
         <v>5</v>
       </c>
       <c r="H29" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
+        <v>2000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3300</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2722,8 +2783,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2740,12 +2801,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>42100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2758,8 +2819,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2856,8 +2920,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2954,50 +3021,53 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3040,118 +3110,124 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
+      <c r="AE32" s="3">
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>11700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>43400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-43800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>24500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3248,209 +3324,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>11700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>43400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-43800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>24500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3485,8 +3570,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3521,106 +3607,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E41" s="3">
         <v>150100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>149900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>265800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>254600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>246900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>229400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>256200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>254400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>314600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>305800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>439100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>408300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>453800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>373900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>377000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>256300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>263200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>94100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>82800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>48900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>34600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>58400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24900</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3717,195 +3807,201 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E43" s="3">
         <v>74300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>86900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>76600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>78900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>80000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>63800</v>
       </c>
       <c r="K43" s="3">
         <v>63800</v>
       </c>
       <c r="L43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="M43" s="3">
         <v>62200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>54700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>60000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>49700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>44500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>50700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>57400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>38900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>45100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>41700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>43200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>39100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>38200</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E44" s="3">
         <v>118600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>119900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>120600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>120900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>123500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>123200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>129500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>127400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>123700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>124600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>120900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>119500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>111300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>111700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>117900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>130400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>127600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>111900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>105700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>111900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>116000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>99300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>94900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>93700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>89400</v>
       </c>
       <c r="AE44" s="3">
         <v>89400</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
+      <c r="AF44" s="3">
+        <v>89400</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>5</v>
@@ -3913,212 +4009,221 @@
       <c r="AH44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E45" s="3">
         <v>36000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>41400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>27600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>30800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>24800</v>
       </c>
       <c r="AB45" s="3">
         <v>24800</v>
       </c>
       <c r="AC45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AD45" s="3">
         <v>23900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>22700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>22000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>364400</v>
+      </c>
+      <c r="E46" s="3">
         <v>378900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>396700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>500100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>494300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>486500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>473800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>477100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>480500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>532600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>514600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>646400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>608400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>657000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>566700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>555400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>453100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>441200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>234600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>278600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>270900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>270100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>214700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>211100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>199400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>218600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>162500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>178800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>174400</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
-        <v>900</v>
+      <c r="D47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>900</v>
@@ -4126,8 +4231,8 @@
       <c r="G47" s="3">
         <v>900</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
+      <c r="H47" s="3">
+        <v>900</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
@@ -4144,8 +4249,8 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4207,204 +4312,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>771500</v>
+      </c>
+      <c r="E48" s="3">
         <v>768100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>769100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>760800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>765800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>751600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>742600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>738300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>723000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>712300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>701300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>678200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>679200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>679800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>681400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>666200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>681600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>693500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>714900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>716200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>715900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>695300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>355100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>340600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>328000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>311000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>302300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>290700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>281300</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>977500</v>
+      </c>
+      <c r="E49" s="3">
         <v>977900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>978400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>978900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1049100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1050900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1052800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1054600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1056400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1058300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1060200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1062100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1063900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1065800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1067700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1069500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1071400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1073200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1075100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1077000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1078800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1080600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1082700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4501,8 +4615,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4599,106 +4716,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E52" s="3">
         <v>30500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10500</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4795,106 +4918,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2146300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2155400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2172500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2266400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2333900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2312400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2291200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2291700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2278300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2325500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2293100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2405500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2369200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2419800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2333500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2307500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2219000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2218700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2032700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2078400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2071800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2053100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1661400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4929,8 +5058,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4965,195 +5095,199 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E57" s="3">
         <v>60800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>65300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>69000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>70000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>69400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>64300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>76100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>77700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>79800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>64900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>68600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>52400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>60000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>47100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>43600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>30900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>46100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>35700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>33600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34400</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>312900</v>
+      </c>
+      <c r="E58" s="3">
         <v>10300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>4700</v>
       </c>
       <c r="L58" s="3">
         <v>4700</v>
       </c>
       <c r="M58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N58" s="3">
         <v>4000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>13700</v>
-      </c>
-      <c r="W58" s="3">
-        <v>8500</v>
       </c>
       <c r="X58" s="3">
         <v>8500</v>
       </c>
       <c r="Y58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>7600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>7300</v>
       </c>
       <c r="AC58" s="3">
         <v>7300</v>
       </c>
       <c r="AD58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AE58" s="3">
         <v>9600</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
+      <c r="AF58" s="3">
+        <v>9600</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>5</v>
@@ -5161,400 +5295,415 @@
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300300</v>
+      </c>
+      <c r="E59" s="3">
         <v>303900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>319700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>288600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>283900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>274900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>263700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>279100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>271300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>275500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>268300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>288500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>275900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>260200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>283900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>256200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>224000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>218600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>244800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>232700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>244100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>160400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>158500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>148800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>168200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>169500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>176000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>167900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>663200</v>
+      </c>
+      <c r="E60" s="3">
         <v>375000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>397700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>373500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>363200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>361800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>344300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>336600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>353800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>345400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>343800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>348800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>370500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>359800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>328700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>356000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>311900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>287500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>273200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>303900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>288300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>297700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>211700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>197200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>189300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>221700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>211300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>219200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211900</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>143900</v>
+      </c>
+      <c r="E61" s="3">
         <v>448600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>450800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>552200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>555200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>563700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>563400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>564200</v>
       </c>
       <c r="K61" s="3">
         <v>564200</v>
       </c>
       <c r="L61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="M61" s="3">
         <v>564700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>566100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>615600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>616200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>733700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>651800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>648100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>644900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>713200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>555900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>584300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>579100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>578400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>570500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>566900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>562000</v>
       </c>
       <c r="AC61" s="3">
         <v>562000</v>
       </c>
       <c r="AD61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>912700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>913300</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>495800</v>
+      </c>
+      <c r="E62" s="3">
         <v>490400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>494600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>507100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>490200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>482500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>484000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>468700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>464700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>457200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>452500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>444200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>438800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>446600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>438400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>441200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>431900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>427200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>424800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>430000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>414400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>136000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>138400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>154000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>149600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>154100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>202400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>202000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5651,8 +5800,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5749,8 +5901,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5847,106 +6002,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1302900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1314000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1343100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1426100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1425500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1415600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1390100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1384800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1386700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1374800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1367100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1416900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1430900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1532300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1427000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1442600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1398100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1432600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1256300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1313000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1297400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1290500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>918200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>902500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>909900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>933300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>927300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5981,8 +6142,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6079,8 +6241,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6177,8 +6342,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6275,8 +6443,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6373,106 +6544,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E72" s="3">
         <v>266300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>254600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>270600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>344400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>338800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>320500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>329800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>318300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>308500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>278400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>272200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>231200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>193600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>142900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>107800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>72500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>116300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>107100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>103200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>102000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>91800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>74800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>100100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>94300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>81200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>32200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6569,8 +6746,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6667,8 +6847,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6765,106 +6948,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>843400</v>
+      </c>
+      <c r="E76" s="3">
         <v>841300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>829400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>840400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>908400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>896700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>901100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>906900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>891700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>950700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>926000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>988600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>938300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>887500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>906500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>865000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>820900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>786200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>776400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>765500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>774400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>762600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>743200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>758200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>729600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>711300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>654600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>254600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>249500</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6961,209 +7150,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>11700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>43400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-43800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>24500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7198,106 +7396,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>25300</v>
+        <v>23100</v>
       </c>
       <c r="E83" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F83" s="3">
         <v>27300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>25200</v>
       </c>
       <c r="L83" s="3">
         <v>25200</v>
       </c>
       <c r="M83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="N83" s="3">
         <v>24500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>21900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>23700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>14400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7394,8 +7596,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7492,8 +7697,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7590,8 +7798,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7688,8 +7899,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7786,106 +8000,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E89" s="3">
         <v>24000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>25100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>92200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>97700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>132300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-14600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>86100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>51700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>36300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>83000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>77800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>28300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>21400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>46500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7920,106 +8140,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-24400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8116,8 +8340,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8214,106 +8441,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-24700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8348,8 +8581,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8438,16 +8672,19 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8544,8 +8781,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8642,8 +8882,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8740,106 +8983,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-73700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-122300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-115400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>20800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>150600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8936,102 +9185,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-116100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-60400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-133600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>80200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>120800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>223800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-55000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>55900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>54800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>25400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,450 +656,463 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>451500</v>
+      </c>
+      <c r="E8" s="3">
         <v>451700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>482800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>506400</v>
       </c>
-      <c r="G8" s="3">
-        <v>532400</v>
-      </c>
       <c r="H8" s="3">
+        <v>438800</v>
+      </c>
+      <c r="I8" s="3">
         <v>431800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>464800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>468900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>499200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>509600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>527700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>477900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>518000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>549500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>534200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>496700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>485400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>260000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>469700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>401800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>431900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>429500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>461200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>355900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>387400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>385500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>408000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>321800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>346100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>337500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>369900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>277100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E9" s="3">
         <v>193600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>195500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>247000</v>
       </c>
-      <c r="G9" s="3">
-        <v>252000</v>
-      </c>
       <c r="H9" s="3">
+        <v>183800</v>
+      </c>
+      <c r="I9" s="3">
         <v>180300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>186100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>222200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>232800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>234600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>236000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>217700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>226500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>235900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>224700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>216500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>210800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>140800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>218600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>187500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>204500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>202500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>212000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>173500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>182600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>177100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>180500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>152400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>162400</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>130300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>258100</v>
+        <v>261600</v>
       </c>
       <c r="E10" s="3">
-        <v>287300</v>
+        <v>258200</v>
       </c>
       <c r="F10" s="3">
+        <v>287200</v>
+      </c>
+      <c r="G10" s="3">
         <v>259400</v>
       </c>
-      <c r="G10" s="3">
-        <v>280400</v>
-      </c>
       <c r="H10" s="3">
+        <v>255000</v>
+      </c>
+      <c r="I10" s="3">
         <v>251500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>278700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>246700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>266400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>275000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>291700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>260200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>291500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>313600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>309500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>280200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>274600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>119200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>251100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>214300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>227400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>227000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>249200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>182400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>204800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>208400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>227500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>169400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>183700</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>146800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1135,8 +1148,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1236,8 +1250,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,109 +1354,115 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5500</v>
+        <v>12900</v>
       </c>
       <c r="E14" s="3">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="G14" s="3">
-        <v>83100</v>
+        <v>900</v>
       </c>
       <c r="H14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>13300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>3100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>8000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>7100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1447,100 +1470,103 @@
         <v>22700</v>
       </c>
       <c r="E15" s="3">
-        <v>23600</v>
+        <v>22700</v>
       </c>
       <c r="F15" s="3">
+        <v>23200</v>
+      </c>
+      <c r="G15" s="3">
         <v>24100</v>
       </c>
-      <c r="G15" s="3">
-        <v>24400</v>
-      </c>
       <c r="H15" s="3">
-        <v>24000</v>
+        <v>22500</v>
       </c>
       <c r="I15" s="3">
-        <v>22300</v>
+        <v>22100</v>
       </c>
       <c r="J15" s="3">
+        <v>22000</v>
+      </c>
+      <c r="K15" s="3">
         <v>24700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24900</v>
-      </c>
-      <c r="L15" s="3">
-        <v>25200</v>
       </c>
       <c r="M15" s="3">
         <v>25200</v>
       </c>
       <c r="N15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="O15" s="3">
         <v>24500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>23600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>21900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>24800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>23700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>22300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>20400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>20300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>19300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>17900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>17600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>15400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>14600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>14400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>13800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1573,210 +1599,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>451100</v>
+        <v>446600</v>
       </c>
       <c r="E17" s="3">
-        <v>459400</v>
+        <v>447600</v>
       </c>
       <c r="F17" s="3">
-        <v>520300</v>
+        <v>454300</v>
       </c>
       <c r="G17" s="3">
-        <v>607000</v>
+        <v>519400</v>
       </c>
       <c r="H17" s="3">
-        <v>426200</v>
+        <v>433800</v>
       </c>
       <c r="I17" s="3">
-        <v>437000</v>
+        <v>425300</v>
       </c>
       <c r="J17" s="3">
+        <v>436700</v>
+      </c>
+      <c r="K17" s="3">
         <v>478700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>483800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>491200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>490400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>469900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>467300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>494700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>472700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>439800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>430600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>301600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>452800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>393400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>430600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>407700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>428800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>377800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>389500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>360600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>369100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>327600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>329500</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>280500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>600</v>
+        <v>4900</v>
       </c>
       <c r="E18" s="3">
-        <v>23400</v>
+        <v>4100</v>
       </c>
       <c r="F18" s="3">
-        <v>-13900</v>
+        <v>28400</v>
       </c>
       <c r="G18" s="3">
-        <v>-74600</v>
+        <v>-13000</v>
       </c>
       <c r="H18" s="3">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="I18" s="3">
-        <v>27800</v>
+        <v>6500</v>
       </c>
       <c r="J18" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>37300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>54800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>61500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>56900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>54800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-41600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>38900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16600</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1812,53 +1845,54 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-800</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1901,424 +1935,439 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
+      <c r="AF20" s="3">
+        <v>0</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>23100</v>
+        <v>27600</v>
       </c>
       <c r="E21" s="3">
-        <v>46000</v>
+        <v>26800</v>
       </c>
       <c r="F21" s="3">
-        <v>12600</v>
+        <v>51700</v>
       </c>
       <c r="G21" s="3">
-        <v>-50400</v>
+        <v>8400</v>
       </c>
       <c r="H21" s="3">
-        <v>32200</v>
+        <v>27500</v>
       </c>
       <c r="I21" s="3">
-        <v>51200</v>
+        <v>28500</v>
       </c>
       <c r="J21" s="3">
+        <v>50100</v>
+      </c>
+      <c r="K21" s="3">
         <v>15900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>45900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>43300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>70300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>70700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>69500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>85000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>79500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>77000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-19700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>32000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>23700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>52800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>42600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>56700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>10400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2700</v>
+        <v>4100</v>
       </c>
       <c r="E22" s="3">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="F22" s="3">
-        <v>3100</v>
+        <v>4300</v>
       </c>
       <c r="G22" s="3">
-        <v>3500</v>
+        <v>1200</v>
       </c>
       <c r="H22" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="I22" s="3">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="J22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K22" s="3">
         <v>3600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3700</v>
       </c>
       <c r="L22" s="3">
         <v>3700</v>
       </c>
       <c r="M22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N22" s="3">
         <v>3600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>700</v>
       </c>
       <c r="P22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>9400</v>
       </c>
       <c r="AB22" s="3">
         <v>9400</v>
       </c>
       <c r="AC22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AD22" s="3">
         <v>9300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>9700</v>
       </c>
       <c r="AI22" s="3">
         <v>9700</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-78300</v>
-      </c>
       <c r="H23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I23" s="3">
         <v>3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>42300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-57200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>25500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
-        <v>-4500</v>
-      </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-13400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-7700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2418,210 +2467,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-73800</v>
-      </c>
       <c r="H26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I26" s="3">
         <v>3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>41000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>43400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-43800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>17400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>24500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1000</v>
+        <v>-8500</v>
       </c>
       <c r="E27" s="3">
-        <v>11800</v>
+        <v>-3100</v>
       </c>
       <c r="F27" s="3">
+        <v>11700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-16000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-73800</v>
       </c>
-      <c r="H27" s="3">
-        <v>3600</v>
-      </c>
       <c r="I27" s="3">
-        <v>15000</v>
+        <v>5600</v>
       </c>
       <c r="J27" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-9300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>41000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>43400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-43800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>17400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>24500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2721,37 +2779,40 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="I29" s="3">
         <v>2000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>3300</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2786,8 +2847,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2804,12 +2865,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>42100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2822,8 +2883,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2923,8 +2987,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3024,53 +3091,56 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>800</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3113,121 +3183,127 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
+      <c r="AF32" s="3">
+        <v>0</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>43400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-43800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>24500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>26000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3327,215 +3403,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>43400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-43800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>24500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>26000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3571,8 +3656,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3608,109 +3694,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E41" s="3">
         <v>179500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>150100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>265800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>254600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>246900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>229400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>256200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>254400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>314600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>305800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>439100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>408300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>453800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>373900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>377000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>256300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>263200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>94100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>82800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>17100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>48900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>58400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24900</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3718,22 +3808,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3810,201 +3900,207 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E43" s="3">
         <v>61100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>74300</v>
       </c>
-      <c r="F43" s="3">
-        <v>86900</v>
-      </c>
       <c r="G43" s="3">
-        <v>76600</v>
+        <v>87800</v>
       </c>
       <c r="H43" s="3">
+        <v>80900</v>
+      </c>
+      <c r="I43" s="3">
         <v>78900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>80000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79900</v>
-      </c>
-      <c r="K43" s="3">
-        <v>63800</v>
       </c>
       <c r="L43" s="3">
         <v>63800</v>
       </c>
       <c r="M43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="N43" s="3">
         <v>62200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>54100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>60000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>44500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>38900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>45100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>41700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>43200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>39100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>38200</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E44" s="3">
         <v>91000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>118600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>119900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>120600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>120900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>123500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>123200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>122000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>129500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>127400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>123700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>124600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>120900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>119500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>111300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>111700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>117900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>130400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>127600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>111900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>105700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>111900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>116000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>99300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>94900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>93700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>89400</v>
       </c>
       <c r="AF44" s="3">
         <v>89400</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
+      <c r="AG44" s="3">
+        <v>89400</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>5</v>
@@ -4012,233 +4108,242 @@
       <c r="AI44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>32900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>36000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>40000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>37000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>39900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>36000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>41400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>24800</v>
       </c>
       <c r="AC45" s="3">
         <v>24800</v>
       </c>
       <c r="AD45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AE45" s="3">
         <v>23900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>22700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>22000</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>243700</v>
+      </c>
+      <c r="E46" s="3">
         <v>364400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>378900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>396700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>500100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>494300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>486500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>473800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>477100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>480500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>532600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>514600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>646400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>608400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>657000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>566700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>555400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>453100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>441200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>234600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>278600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>270900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>270100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>214700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>211100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>199400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>218600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>162500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>178800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>174400</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
-        <v>900</v>
+        <v>2800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G47" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="H47" s="3">
         <v>900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+      <c r="I47" s="3">
+        <v>900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1900</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -4252,8 +4357,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4315,210 +4420,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>774200</v>
+      </c>
+      <c r="E48" s="3">
         <v>771500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>768100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>769100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>760800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>765800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>751600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>742600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>738300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>723000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>712300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>701300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>678200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>679200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>679800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>681400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>666200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>681600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>693500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>714900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>716200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>715900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>695300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>355100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>340600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>328000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>311000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>302300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>290700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>281300</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>966500</v>
+      </c>
+      <c r="E49" s="3">
         <v>977500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>977900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>978400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>978900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1049100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1050900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1052800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1054600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1056400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1058300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1060200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1062100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1063900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1065800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1067700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1069500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1071400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1073200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1075100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1077000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1078800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1080600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4618,8 +4732,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4719,109 +4836,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>30600</v>
+        <v>32900</v>
       </c>
       <c r="E52" s="3">
+        <v>29600</v>
+      </c>
+      <c r="F52" s="3">
         <v>30500</v>
       </c>
-      <c r="F52" s="3">
-        <v>27400</v>
-      </c>
       <c r="G52" s="3">
+        <v>26500</v>
+      </c>
+      <c r="H52" s="3">
         <v>25800</v>
       </c>
-      <c r="H52" s="3">
-        <v>23900</v>
-      </c>
       <c r="I52" s="3">
-        <v>23400</v>
+        <v>21900</v>
       </c>
       <c r="J52" s="3">
+        <v>21500</v>
+      </c>
+      <c r="K52" s="3">
         <v>22000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10500</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4921,109 +5044,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2020100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2146300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2155400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2172500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2266400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2333900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2312400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2291200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2291700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2278300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2325500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2293100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2405500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2369200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2419800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2333500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2307500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2219000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2218700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2032700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2078400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2071800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2053100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5059,8 +5188,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5096,201 +5226,205 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E57" s="3">
         <v>50000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>60800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>64100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>65300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>70000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>69400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>64300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>76100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>77700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>79800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>64900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>68600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>52400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>60000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>45300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>47100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>43600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>30900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>46100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>35700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>33600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>34400</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>312900</v>
+        <v>189900</v>
       </c>
       <c r="E58" s="3">
-        <v>10300</v>
+        <v>399900</v>
       </c>
       <c r="F58" s="3">
-        <v>10500</v>
+        <v>96600</v>
       </c>
       <c r="G58" s="3">
-        <v>10600</v>
+        <v>95900</v>
       </c>
       <c r="H58" s="3">
-        <v>10500</v>
+        <v>93100</v>
       </c>
       <c r="I58" s="3">
-        <v>3200</v>
+        <v>82300</v>
       </c>
       <c r="J58" s="3">
+        <v>75300</v>
+      </c>
+      <c r="K58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>4700</v>
       </c>
       <c r="M58" s="3">
         <v>4700</v>
       </c>
       <c r="N58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O58" s="3">
         <v>4000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>13800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13700</v>
-      </c>
-      <c r="X58" s="3">
-        <v>8500</v>
       </c>
       <c r="Y58" s="3">
         <v>8500</v>
       </c>
       <c r="Z58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AA58" s="3">
         <v>7600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>7300</v>
       </c>
       <c r="AD58" s="3">
         <v>7300</v>
       </c>
       <c r="AE58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AF58" s="3">
         <v>9600</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
+      <c r="AG58" s="3">
+        <v>9600</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
@@ -5298,412 +5432,427 @@
       <c r="AI58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300300</v>
+        <v>146400</v>
       </c>
       <c r="E59" s="3">
-        <v>303900</v>
+        <v>150500</v>
       </c>
       <c r="F59" s="3">
-        <v>319700</v>
+        <v>165600</v>
       </c>
       <c r="G59" s="3">
-        <v>300000</v>
+        <v>150600</v>
       </c>
       <c r="H59" s="3">
-        <v>288600</v>
+        <v>147600</v>
       </c>
       <c r="I59" s="3">
+        <v>148500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>163000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>274900</v>
+      </c>
+      <c r="L59" s="3">
+        <v>263700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>279100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>271300</v>
+      </c>
+      <c r="O59" s="3">
+        <v>275500</v>
+      </c>
+      <c r="P59" s="3">
+        <v>268300</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>288500</v>
+      </c>
+      <c r="R59" s="3">
+        <v>275900</v>
+      </c>
+      <c r="S59" s="3">
+        <v>260200</v>
+      </c>
+      <c r="T59" s="3">
         <v>283900</v>
       </c>
-      <c r="J59" s="3">
-        <v>274900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>263700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>279100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>271300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>275500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>268300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>288500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>275900</v>
-      </c>
-      <c r="R59" s="3">
-        <v>260200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>283900</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>256200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>224000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>218600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>244800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>232700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>244100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>160400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>158500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>148800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>168200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>169500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>176000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>167900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>426100</v>
+      </c>
+      <c r="E60" s="3">
         <v>663200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>375000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>397700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>373500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>363200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>361800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>344300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>336600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>353800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>345400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>343800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>348800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>370500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>359800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>328700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>356000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>311900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>287500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>273200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>303900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>288300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>297700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>211700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>197200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>189300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>221700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>219200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>211900</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>143900</v>
+        <v>641500</v>
       </c>
       <c r="E61" s="3">
-        <v>448600</v>
+        <v>526500</v>
       </c>
       <c r="F61" s="3">
-        <v>450800</v>
+        <v>828700</v>
       </c>
       <c r="G61" s="3">
-        <v>552200</v>
+        <v>827600</v>
       </c>
       <c r="H61" s="3">
-        <v>555200</v>
+        <v>927000</v>
       </c>
       <c r="I61" s="3">
-        <v>563700</v>
+        <v>935900</v>
       </c>
       <c r="J61" s="3">
+        <v>935400</v>
+      </c>
+      <c r="K61" s="3">
         <v>563400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>564200</v>
       </c>
       <c r="L61" s="3">
         <v>564200</v>
       </c>
       <c r="M61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="N61" s="3">
         <v>564700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>566100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>615600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>616200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>733700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>651800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>648100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>644900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>713200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>555900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>584300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>579100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>578400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>570500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>566900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>562000</v>
       </c>
       <c r="AD61" s="3">
         <v>562000</v>
       </c>
       <c r="AE61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>912700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>913300</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>495800</v>
+        <v>8800</v>
       </c>
       <c r="E62" s="3">
-        <v>490400</v>
+        <v>8400</v>
       </c>
       <c r="F62" s="3">
-        <v>494600</v>
+        <v>8400</v>
       </c>
       <c r="G62" s="3">
-        <v>500400</v>
+        <v>8500</v>
       </c>
       <c r="H62" s="3">
-        <v>507100</v>
+        <v>9800</v>
       </c>
       <c r="I62" s="3">
-        <v>490200</v>
+        <v>9300</v>
       </c>
       <c r="J62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K62" s="3">
         <v>482500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>484000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>468700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>464700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>457200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>452500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>444200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>438800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>446600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>438400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>441200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>431900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>427200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>424800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>430000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>414400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>136000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>138400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>154000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>149600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>154100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>202400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>202000</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5803,8 +5952,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5904,8 +6056,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6005,109 +6160,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1180100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1302900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1314000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1343100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1426100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1425500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1415600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1390100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1384800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1386700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1374800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1367100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1416900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1430900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1532300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1427000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1442600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1398100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1432600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1256300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1313000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1297400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1290500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>918200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>902500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>909900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>933300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>927300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6143,8 +6304,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6244,8 +6406,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6345,8 +6510,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6446,8 +6614,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6547,109 +6718,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E72" s="3">
         <v>263200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>266300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>254600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>270600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>344400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>338800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>320500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>329800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>318300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>308500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>278400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>272200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>231200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>193600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>142900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>107800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>72500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>116300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>107100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>103200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>102000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>91800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>74800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>100100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>94300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>81200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>32200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6900</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6749,8 +6926,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6850,8 +7030,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6951,109 +7134,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E76" s="3">
         <v>843400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>841300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>829400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>840400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>908400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>896700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>901100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>906900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>891700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>950700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>926000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>988600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>938300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>887500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>906500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>865000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>820900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>786200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>776400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>765500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>774400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>762600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>743200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>758200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>729600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>711300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>654600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>254600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>249500</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7153,215 +7342,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>43400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-43800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>24500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>26000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7397,109 +7595,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>23100</v>
+        <v>24400</v>
       </c>
       <c r="E83" s="3">
-        <v>24200</v>
+        <v>23400</v>
       </c>
       <c r="F83" s="3">
-        <v>27300</v>
+        <v>24400</v>
       </c>
       <c r="G83" s="3">
-        <v>24400</v>
+        <v>22800</v>
       </c>
       <c r="H83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>23400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>24700</v>
+      </c>
+      <c r="L83" s="3">
         <v>24900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>24800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>24700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>24900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>25200</v>
       </c>
       <c r="M83" s="3">
         <v>25200</v>
       </c>
       <c r="N83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="O83" s="3">
         <v>24500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>23700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>22300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>14600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>14400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7599,8 +7801,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7700,8 +7905,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7801,8 +8009,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7902,8 +8113,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8003,109 +8217,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E89" s="3">
         <v>51500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>47100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>25100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>92200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>97700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>132300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-14600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>86100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>51700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>36300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>83000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>77800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>28300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>21400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>46500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8141,109 +8361,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-36000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-24900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8343,8 +8567,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8444,109 +8671,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-33200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8582,31 +8815,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8675,16 +8909,19 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8784,8 +9021,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8885,8 +9125,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8986,132 +9229,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-73700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-122300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-115400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>20800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>150600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-24400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9188,105 +9437,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-98300</v>
+      </c>
+      <c r="E102" s="3">
         <v>29400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-116100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-60400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-133600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>80200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>120800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>223800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-55000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>55900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>54800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>25400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,463 +656,475 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>437300</v>
+      </c>
+      <c r="E8" s="3">
         <v>451500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>451700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>482800</v>
       </c>
-      <c r="G8" s="3">
-        <v>506400</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
         <v>438800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>431800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>464800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>468900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>499200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>509600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>527700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>477900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>518000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>549500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>534200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>496700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>485400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>260000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>469700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>401800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>431900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>429500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>461200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>355900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>387400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>385500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>408000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>321800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>346100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>337500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>369900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>277100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E9" s="3">
         <v>189900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>193600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>195500</v>
       </c>
-      <c r="G9" s="3">
-        <v>247000</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
         <v>183800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>180300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>186100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>222200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>232800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>234600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>236000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>217700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>226500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>235900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>224700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>216500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>210800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>140800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>218600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>187500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>204500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>202500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>212000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>173500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>182600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>177100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>180500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>152400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>162400</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>130300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>252300</v>
+      </c>
+      <c r="E10" s="3">
         <v>261600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>258200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>287200</v>
       </c>
-      <c r="G10" s="3">
-        <v>259400</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
         <v>255000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>251500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>278700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>246700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>266400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>275000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>291700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>260200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>291500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>313600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>309500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>280200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>274600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>119200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>251100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>214300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>227400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>227000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>249200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>182400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>204800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>208400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>227500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>169400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>183700</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>146800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1149,8 +1161,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1253,8 +1266,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1357,112 +1373,118 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E14" s="3">
         <v>12900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="K14" s="3">
+        <v>400</v>
+      </c>
+      <c r="L14" s="3">
+        <v>500</v>
+      </c>
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
-        <v>900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>400</v>
-      </c>
-      <c r="K14" s="3">
-        <v>500</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O14" s="3">
+        <v>600</v>
+      </c>
+      <c r="P14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>700</v>
+      </c>
+      <c r="R14" s="3">
+        <v>800</v>
+      </c>
+      <c r="S14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U14" s="3">
+        <v>7200</v>
+      </c>
+      <c r="V14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W14" s="3">
+        <v>15800</v>
+      </c>
+      <c r="X14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
-        <v>3700</v>
-      </c>
-      <c r="N14" s="3">
-        <v>600</v>
-      </c>
-      <c r="O14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>800</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>7200</v>
-      </c>
-      <c r="U14" s="3">
-        <v>2400</v>
-      </c>
-      <c r="V14" s="3">
-        <v>15800</v>
-      </c>
-      <c r="W14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>13300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>3100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>8000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1473,100 +1495,103 @@
         <v>22700</v>
       </c>
       <c r="F15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="G15" s="3">
         <v>23200</v>
       </c>
-      <c r="G15" s="3">
-        <v>24100</v>
-      </c>
       <c r="H15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I15" s="3">
         <v>22500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24900</v>
-      </c>
-      <c r="M15" s="3">
-        <v>25200</v>
       </c>
       <c r="N15" s="3">
         <v>25200</v>
       </c>
       <c r="O15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="P15" s="3">
         <v>24500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>25100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>24000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>23600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>22200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>21900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>24800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>23700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>22300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>20800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>20400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>20300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>19300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>17600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>17900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>17600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>15400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>14600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>14400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1600,216 +1625,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>440700</v>
+      </c>
+      <c r="E17" s="3">
         <v>446600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>447600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>454300</v>
       </c>
-      <c r="G17" s="3">
-        <v>519400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
         <v>433800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>425300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>436700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>478700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>483800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>491200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>490400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>469900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>467300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>494700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>472700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>439800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>430600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>301600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>452800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>393400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>430600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>407700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>428800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>377800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>389500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>360600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>369100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>327600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>329500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>280500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
         <v>5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>37300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>50700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>61500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>56900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>54800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-41600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>21800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>32400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>38900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16600</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1846,8 +1878,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1860,8 +1893,8 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="3">
-        <v>2700</v>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
@@ -1872,30 +1905,30 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1938,436 +1971,451 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
+      <c r="AG20" s="3">
+        <v>0</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E21" s="3">
         <v>27600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51700</v>
       </c>
-      <c r="G21" s="3">
-        <v>8400</v>
-      </c>
       <c r="H21" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I21" s="3">
         <v>27500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>50100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>43300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>70300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>69500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>85000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>79500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>77000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-19700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>32000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>23700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>52800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>17300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>56700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E22" s="3">
         <v>4100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4300</v>
       </c>
-      <c r="G22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
         <v>3700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3700</v>
       </c>
       <c r="M22" s="3">
         <v>3700</v>
       </c>
       <c r="N22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O22" s="3">
         <v>3600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
       </c>
       <c r="Q22" s="3">
+        <v>700</v>
+      </c>
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>9400</v>
       </c>
       <c r="AC22" s="3">
         <v>9400</v>
       </c>
       <c r="AD22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AE22" s="3">
         <v>9300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>14600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>9700</v>
       </c>
       <c r="AJ22" s="3">
         <v>9700</v>
       </c>
+      <c r="AK22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-17800</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>45000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>42300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-57200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>29500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>25500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-13400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>8500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2470,216 +2518,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>41000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>43400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-43800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>24500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1500</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
         <v>-73800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>41000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>43400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-43800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>24500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1500</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2782,40 +2839,43 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-2100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-73400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>2000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>3300</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2850,8 +2910,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2868,12 +2928,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>42100</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2886,8 +2946,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2990,8 +3053,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3094,8 +3160,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3108,8 +3177,8 @@
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2700</v>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
@@ -3120,30 +3189,30 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3186,124 +3255,130 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
+      <c r="AG32" s="3">
+        <v>0</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
         <v>-73800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>41000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>43400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-43800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>26000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3406,221 +3481,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3">
         <v>-73800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>41000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>43400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-43800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>26000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3657,8 +3741,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3695,112 +3780,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E41" s="3">
         <v>81200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>179500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>150100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>149900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>265800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>254600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>246900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>229400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>256200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>254400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>314600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>305800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>439100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>408300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>453800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>373900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>377000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>256300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>263200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>39300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>94100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>82800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>72500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>48900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>58400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24900</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3808,26 +3897,26 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3903,207 +3992,213 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E43" s="3">
         <v>46800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>74300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>87800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>80900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>78900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>80000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79900</v>
-      </c>
-      <c r="L43" s="3">
-        <v>63800</v>
       </c>
       <c r="M43" s="3">
         <v>63800</v>
       </c>
       <c r="N43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="O43" s="3">
         <v>62200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>44500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>58000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>50700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>38900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>45100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>41700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>43200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>39100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>38200</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E44" s="3">
         <v>87600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>91000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>118600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>119900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>120600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>120900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>123500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>123200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>129500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>127400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>123700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>124600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>120900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>119500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>111300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>111700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>117900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>130400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>127600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>111900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>105700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>111900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>116000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>99300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>94900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>93700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>89400</v>
       </c>
       <c r="AG44" s="3">
         <v>89400</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
+      <c r="AH44" s="3">
+        <v>89400</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>5</v>
@@ -4111,8 +4206,11 @@
       <c r="AJ44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4137,217 +4235,223 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>41400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>27600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>24800</v>
       </c>
       <c r="AD45" s="3">
         <v>24800</v>
       </c>
       <c r="AE45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>23900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>22700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>22000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>249800</v>
+      </c>
+      <c r="E46" s="3">
         <v>243700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>364400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>378900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>396700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>494300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>486500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>473800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>477100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>480500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>532600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>514600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>646400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>608400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>657000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>566700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>555400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>453100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>441200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>234600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>278600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>270900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>270100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>214700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>211100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>199400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>218600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>162500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>178800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>174400</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>1800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>900</v>
       </c>
       <c r="I47" s="3">
         <v>900</v>
       </c>
       <c r="J47" s="3">
+        <v>900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4360,8 +4464,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4423,216 +4527,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>770800</v>
+      </c>
+      <c r="E48" s="3">
         <v>774200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>771500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>768100</v>
       </c>
-      <c r="G48" s="3">
-        <v>769100</v>
-      </c>
       <c r="H48" s="3">
+        <v>766500</v>
+      </c>
+      <c r="I48" s="3">
         <v>760800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>765800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>751600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>742600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>738300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>723000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>712300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>701300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>678200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>679200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>679800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>681400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>666200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>681600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>693500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>714900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>716200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>715900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>695300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>355100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>340600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>328000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>311000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>302300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>290700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>281300</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>947100</v>
+      </c>
+      <c r="E49" s="3">
         <v>966500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>977500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>977900</v>
       </c>
-      <c r="G49" s="3">
-        <v>978400</v>
-      </c>
       <c r="H49" s="3">
+        <v>978300</v>
+      </c>
+      <c r="I49" s="3">
         <v>978900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1049100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1050900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1052800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1054600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1056400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1058300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1060200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1062100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1063900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1065800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1067700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1069500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1071400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1073200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1075100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1077000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1078800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1080600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4735,8 +4848,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4839,112 +4955,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E52" s="3">
         <v>32900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30500</v>
       </c>
-      <c r="G52" s="3">
-        <v>26500</v>
-      </c>
       <c r="H52" s="3">
+        <v>29300</v>
+      </c>
+      <c r="I52" s="3">
         <v>25800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10500</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5047,112 +5169,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2007800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2020100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2146300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2155400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2172500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2266400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2333900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2312400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2291200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2291700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2278300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2325500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2293100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2405500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2369200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2419800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2333500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2307500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2219000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2218700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2032700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2078400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2071800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2053100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5189,8 +5317,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5227,207 +5356,211 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E57" s="3">
         <v>39600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>64100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>65300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>69000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>70000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>76100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>77700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>79800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>64900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>68600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>52400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>60000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>47100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>45100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>43600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>30900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>46100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>35700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34400</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>201100</v>
+      </c>
+      <c r="E58" s="3">
         <v>189900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>399900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>96600</v>
       </c>
-      <c r="G58" s="3">
-        <v>95900</v>
-      </c>
       <c r="H58" s="3">
+        <v>95600</v>
+      </c>
+      <c r="I58" s="3">
         <v>93100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>82300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>75300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4700</v>
       </c>
       <c r="N58" s="3">
         <v>4700</v>
       </c>
       <c r="O58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P58" s="3">
         <v>4000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13700</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>8500</v>
       </c>
       <c r="Z58" s="3">
         <v>8500</v>
       </c>
       <c r="AA58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AB58" s="3">
         <v>7600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>7300</v>
       </c>
       <c r="AE58" s="3">
         <v>7300</v>
       </c>
       <c r="AF58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AG58" s="3">
         <v>9600</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
+      <c r="AH58" s="3">
+        <v>9600</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>5</v>
@@ -5435,424 +5568,439 @@
       <c r="AJ58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E59" s="3">
         <v>146400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>150500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>165600</v>
       </c>
-      <c r="G59" s="3">
-        <v>150600</v>
-      </c>
       <c r="H59" s="3">
+        <v>150900</v>
+      </c>
+      <c r="I59" s="3">
         <v>147600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>148500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>163000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>274900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>263700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>279100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>271300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>275500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>268300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>288500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>275900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>260200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>283900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>256200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>224000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>218600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>244800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>232700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>244100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>160400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>158500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>148800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>168200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>169500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>176000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>167900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>468300</v>
+      </c>
+      <c r="E60" s="3">
         <v>426100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>663200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>375000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>397700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>373500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>363200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>361800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>344300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>336600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>353800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>345400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>343800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>348800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>370500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>359800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>328700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>356000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>311900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>287500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>273200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>303900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>288300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>297700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>211700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>197200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>189300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>221700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>219200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>211900</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>614900</v>
+      </c>
+      <c r="E61" s="3">
         <v>641500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>526500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>828700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>827600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>927000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>935900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>935400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>563400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>564200</v>
       </c>
       <c r="M61" s="3">
         <v>564200</v>
       </c>
       <c r="N61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="O61" s="3">
         <v>564700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>566100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>615600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>616200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>733700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>651800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>648100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>644900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>713200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>555900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>584300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>579100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>578400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>570500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>566900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>562000</v>
       </c>
       <c r="AE61" s="3">
         <v>562000</v>
       </c>
       <c r="AF61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>912700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>913300</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E62" s="3">
         <v>8800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>8400</v>
       </c>
       <c r="F62" s="3">
         <v>8400</v>
       </c>
       <c r="G62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>482500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>484000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>468700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>464700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>457200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>452500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>444200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>438800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>446600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>438400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>441200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>431900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>427200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>424800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>430000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>414400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>136000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>138400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>154000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>149600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>154100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>202400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>202000</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5955,8 +6103,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6059,8 +6210,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6163,112 +6317,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1191400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1180100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1302900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1314000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1343100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1426100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1425500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1415600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1390100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1384800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1386700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1374800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1367100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1416900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1430900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1532300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1427000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1442600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1398100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1432600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1256300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1313000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1297400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1290500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>918200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>902500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>909900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>933300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>927300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6305,8 +6465,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6409,8 +6570,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6513,8 +6677,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6617,8 +6784,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6721,112 +6891,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E72" s="3">
         <v>254700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>263200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>266300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>254600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>270600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>344400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>338800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>320500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>329800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>318300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>308500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>278400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>272200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>231200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>193600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>142900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>107800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>72500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>116300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>107100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>103200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>102000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>91800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>74800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>100100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>94300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>81200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>32200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6929,8 +7105,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7033,8 +7212,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7137,112 +7319,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>816300</v>
+      </c>
+      <c r="E76" s="3">
         <v>840000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>843400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>841300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>829400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>840400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>908400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>896700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>901100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>906900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>891700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>950700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>926000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>988600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>938300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>887500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>906500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>865000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>820900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>786200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>776400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>765500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>774400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>762600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>743200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>758200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>729600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>711300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>654600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>254600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>249500</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7345,221 +7533,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
         <v>-73800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>41000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>43400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-43800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>26000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7596,112 +7793,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3">
         <v>24400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24900</v>
-      </c>
-      <c r="M83" s="3">
-        <v>25200</v>
       </c>
       <c r="N83" s="3">
         <v>25200</v>
       </c>
       <c r="O83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="P83" s="3">
         <v>24500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>21900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>23700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>14600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>14400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7804,8 +8005,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7908,8 +8112,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8012,8 +8219,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8116,8 +8326,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8220,112 +8433,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>27900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>51500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24000</v>
       </c>
-      <c r="G89" s="3">
-        <v>19800</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3">
         <v>41100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>47100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>25100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>92200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>97700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>132300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-14600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>86100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>51700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>36300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>83000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>77800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>28300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>21400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>46500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8362,112 +8581,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-32800</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
         <v>-27800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-12700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8570,8 +8793,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8674,112 +8900,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-33200</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3">
         <v>-27800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-25800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8816,8 +9048,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8842,8 +9075,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8912,16 +9145,19 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9024,8 +9260,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9128,8 +9367,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9232,112 +9474,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5200</v>
       </c>
-      <c r="G100" s="3">
-        <v>-102600</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-73700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-122300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-115400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>20800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>150600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-24400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>8700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9362,8 +9610,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9440,108 +9688,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-98300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
-        <v>-116100</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>11200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-133600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-45700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>80200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>120800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>223800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-55000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>55900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>54800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>25400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,475 +656,488 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>510300</v>
+      </c>
+      <c r="E8" s="3">
         <v>437300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>451500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>451700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>482800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>438800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>431800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>464800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>468900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>499200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>509600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>527700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>477900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>518000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>549500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>534200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>496700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>485400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>260000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>469700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>401800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>431900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>429500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>461200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>355900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>387400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>385500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>408000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>321800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>346100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>337500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>369900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>277100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E9" s="3">
         <v>185000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>189900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>193600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>195500</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
         <v>183800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>180300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>186100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>222200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>232800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>234600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>236000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>217700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>226500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>235900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>224700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>216500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>210800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>140800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>218600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>187500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>204500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>202500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>212000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>173500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>182600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>177100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>180500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>152400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>162400</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>130300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>305100</v>
+      </c>
+      <c r="E10" s="3">
         <v>252300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>261600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>258200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>287200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
         <v>255000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>251500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>278700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>246700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>266400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>275000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>291700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>260200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>291500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>313600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>309500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>280200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>274600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>119200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>251100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>214300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>227400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>227000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>249200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>182400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>204800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>208400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>227500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>169400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>183700</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>146800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1162,8 +1175,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1269,8 +1283,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1376,120 +1393,126 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
         <v>22200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="G14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>13300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>3100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>8000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>7100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>22700</v>
+        <v>23000</v>
       </c>
       <c r="E15" s="3">
         <v>22700</v>
@@ -1498,100 +1521,103 @@
         <v>22700</v>
       </c>
       <c r="G15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="H15" s="3">
         <v>23200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24900</v>
-      </c>
-      <c r="N15" s="3">
-        <v>25200</v>
       </c>
       <c r="O15" s="3">
         <v>25200</v>
       </c>
       <c r="P15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="Q15" s="3">
         <v>24500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>25100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>24000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>23600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>22600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>21900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>24800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>23700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>22300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>20800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>20400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>20300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>19300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>17600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>17900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>17600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>15400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>14600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>13800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1626,222 +1652,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>481600</v>
+      </c>
+      <c r="E17" s="3">
         <v>440700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>446600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>447600</v>
       </c>
-      <c r="G17" s="3">
-        <v>454300</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17" s="3">
+        <v>454400</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
         <v>433800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>425300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>436700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>478700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>483800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>491200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>490400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>469900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>467300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>494700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>472700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>439800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>430600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>301600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>452800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>393400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>430600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>407700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>428800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>377800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>389500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>360600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>369100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>327600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>329500</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>280500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4100</v>
       </c>
-      <c r="G18" s="3">
-        <v>28400</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="H18" s="3">
+        <v>28300</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>50700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>54800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>56900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>54800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-41600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>21800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>38900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>16600</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1879,8 +1912,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1908,30 +1942,30 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1974,127 +2008,133 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
+      <c r="AH20" s="3">
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E21" s="3">
         <v>19300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26800</v>
       </c>
-      <c r="G21" s="3">
-        <v>51700</v>
-      </c>
       <c r="H21" s="3">
+        <v>51600</v>
+      </c>
+      <c r="I21" s="3">
         <v>15700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>50100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>45900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>43300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>70300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>70700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>69500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>85000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>79500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>77000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-19700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>32000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>23700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>52800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>17300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>56700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>31900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>10400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,320 +2142,329 @@
         <v>4600</v>
       </c>
       <c r="E22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
         <v>3700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>3700</v>
       </c>
       <c r="N22" s="3">
         <v>3700</v>
       </c>
       <c r="O22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P22" s="3">
         <v>3600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>700</v>
       </c>
       <c r="R22" s="3">
+        <v>700</v>
+      </c>
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>9400</v>
       </c>
       <c r="AD22" s="3">
         <v>9400</v>
       </c>
       <c r="AE22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>9300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>14900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>9700</v>
       </c>
       <c r="AK22" s="3">
         <v>9700</v>
       </c>
+      <c r="AL22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19200</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>45000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>55100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>42300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-57200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>23300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>29500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>25500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-13400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2521,222 +2570,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11800</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>41000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>43400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>35300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-43800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>24500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1500</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11700</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
         <v>-73800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>41000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>43400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-43800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>24500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1500</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2842,43 +2900,46 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>800</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-2100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-73400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>2000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>3300</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2913,8 +2974,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2931,12 +2992,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>42100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2949,8 +3010,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3056,8 +3120,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3163,8 +3230,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3192,30 +3262,30 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3258,127 +3328,133 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
+      <c r="AH32" s="3">
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11700</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
         <v>-73800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>41000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>43400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-43800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>26000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1500</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3484,227 +3560,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11700</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
         <v>-73800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>41000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>43400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-43800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>26000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1500</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3742,8 +3827,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3781,115 +3867,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E41" s="3">
         <v>73900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>81200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>179500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>150100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>149900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>265800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>254600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>246900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>229400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>256200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>254400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>314600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>305800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>439100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>408300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>453800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>373900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>377000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>256300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>263200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>94100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>82800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>17100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>48900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>34600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>58400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24900</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3900,26 +3990,26 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3995,213 +4085,219 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E43" s="3">
         <v>50800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>74300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>87800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>80900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>78900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>80000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79900</v>
-      </c>
-      <c r="M43" s="3">
-        <v>63800</v>
       </c>
       <c r="N43" s="3">
         <v>63800</v>
       </c>
       <c r="O43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="P43" s="3">
         <v>62200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>60000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>58500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>44500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>58000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>38900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>45100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>41700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>43200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>39100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>38200</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E44" s="3">
         <v>93900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>91000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>118600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>119900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>120600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>120900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>123500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>123200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>122000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>129500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>127400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>123700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>124600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>120900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>119500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>111300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>111700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>117900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>130400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>127600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>111900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>105700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>111900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>116000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>99300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>94900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>93700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>89400</v>
       </c>
       <c r="AH44" s="3">
         <v>89400</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
+      <c r="AI44" s="3">
+        <v>89400</v>
       </c>
       <c r="AJ44" s="3" t="s">
         <v>5</v>
@@ -4209,8 +4305,11 @@
       <c r="AK44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4238,223 +4337,229 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>41400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>30800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>24800</v>
       </c>
       <c r="AE45" s="3">
         <v>24800</v>
       </c>
       <c r="AF45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AG45" s="3">
         <v>23900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>22700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>22000</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>254100</v>
+      </c>
+      <c r="E46" s="3">
         <v>249800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>364400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>378900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>396700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>500100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>494300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>486500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>473800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>477100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>480500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>532600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>514600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>646400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>608400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>657000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>566700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>555400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>453100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>441200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>234600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>278600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>270900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>270100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>214700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>211100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>199400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>218600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>162500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>178800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>174400</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>1800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3300</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>1800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>900</v>
       </c>
       <c r="J47" s="3">
         <v>900</v>
       </c>
       <c r="K47" s="3">
+        <v>900</v>
+      </c>
+      <c r="L47" s="3">
         <v>1900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4467,8 +4572,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4530,222 +4635,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>760400</v>
+      </c>
+      <c r="E48" s="3">
         <v>770800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>774200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>771500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>768100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>766500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>760800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>765800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>751600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>742600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>738300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>723000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>712300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>701300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>678200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>679200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>679800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>681400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>666200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>681600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>693500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>714900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>716200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>715900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>695300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>355100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>340600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>328000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>311000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>302300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>290700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>281300</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>946900</v>
+      </c>
+      <c r="E49" s="3">
         <v>947100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>966500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>977500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>977900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>978300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>978900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1049100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1050900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1052800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1054600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1056400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1058300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1060200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1062100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1063900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1065800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1067700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1069500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1071400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1073200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1075100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1077000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1078800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1080600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4851,8 +4965,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4958,115 +5075,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E52" s="3">
         <v>38300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10500</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5172,115 +5295,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2010400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2007800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2020100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2146300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2155400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2172500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2266400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2333900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2312400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2291200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2291700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2278300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2325500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2293100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2405500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2369200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2419800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2333500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2307500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2219000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2218700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2032700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2078400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2071800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2053100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5318,8 +5447,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5357,213 +5487,217 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E57" s="3">
         <v>53600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>50000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>60800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>64100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>65300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>69000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>70000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>69400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>76100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>77700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>79800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>64900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>52400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>60000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>47100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>45100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>43600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>46100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>35700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>33600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>34400</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>202200</v>
+      </c>
+      <c r="E58" s="3">
         <v>201100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>189900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>399900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>96600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>95600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>93100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>82300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>75300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>4700</v>
       </c>
       <c r="O58" s="3">
         <v>4700</v>
       </c>
       <c r="P58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>4000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13700</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>8500</v>
       </c>
       <c r="AA58" s="3">
         <v>8500</v>
       </c>
       <c r="AB58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AC58" s="3">
         <v>7600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>7300</v>
       </c>
       <c r="AF58" s="3">
         <v>7300</v>
       </c>
       <c r="AG58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AH58" s="3">
         <v>9600</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
+      <c r="AI58" s="3">
+        <v>9600</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>5</v>
@@ -5571,436 +5705,451 @@
       <c r="AK58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>227900</v>
+      </c>
+      <c r="E59" s="3">
         <v>150200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>146400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>150500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>165600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>150900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>147600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>163000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>274900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>263700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>279100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>271300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>275500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>288500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>275900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>260200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>283900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>256200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>224000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>218600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>244800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>232700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>244100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>160400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>158500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>148800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>168200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>169500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>176000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>167900</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>468200</v>
+      </c>
+      <c r="E60" s="3">
         <v>468300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>426100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>663200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>375000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>397700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>373500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>363200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>361800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>344300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>336600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>353800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>345400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>343800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>348800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>370500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>359800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>328700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>356000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>311900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>287500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>273200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>303900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>288300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>297700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>211700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>197200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>189300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>221700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>211300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>219200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>211900</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>602900</v>
+      </c>
+      <c r="E61" s="3">
         <v>614900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>641500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>526500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>828700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>827600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>927000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>935900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>935400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>563400</v>
-      </c>
-      <c r="M61" s="3">
-        <v>564200</v>
       </c>
       <c r="N61" s="3">
         <v>564200</v>
       </c>
       <c r="O61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="P61" s="3">
         <v>564700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>566100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>615600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>616200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>733700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>651800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>648100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>644900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>713200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>555900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>584300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>579100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>578400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>570500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>566900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>562000</v>
       </c>
       <c r="AF61" s="3">
         <v>562000</v>
       </c>
       <c r="AG61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>912700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>913300</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E62" s="3">
         <v>8200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>8400</v>
       </c>
       <c r="G62" s="3">
         <v>8400</v>
       </c>
       <c r="H62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>482500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>484000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>468700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>464700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>457200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>452500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>444200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>438800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>446600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>438400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>441200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>431900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>427200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>424800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>430000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>414400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>136000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>138400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>154000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>149600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>154100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>202400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>202000</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6106,8 +6255,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6213,8 +6365,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6320,115 +6475,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1174200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1191400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1180100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1302900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1314000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1343100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1426100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1425500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1415600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1390100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1384800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1386700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1374800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1367100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1416900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1430900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1532300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1427000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1442600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1398100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1432600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1256300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1313000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1297400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1290500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>918200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>902500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>909900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>933300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>927300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6466,8 +6627,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6573,8 +6735,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6680,8 +6845,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6787,8 +6955,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6894,115 +7065,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>240300</v>
+      </c>
+      <c r="E72" s="3">
         <v>226100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>254700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>263200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>266300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>254600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>270600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>344400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>338800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>320500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>329800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>318300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>308500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>278400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>272200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>231200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>193600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>142900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>107800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>72500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>116300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>107100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>103200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>102000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>91800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>74800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>100100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>94300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>81200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6900</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7108,8 +7285,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7215,8 +7395,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7322,115 +7505,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>836200</v>
+      </c>
+      <c r="E76" s="3">
         <v>816300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>840000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>843400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>841300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>829400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>840400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>908400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>896700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>901100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>906900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>891700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>950700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>926000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>988600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>938300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>887500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>906500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>865000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>820900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>786200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>776400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>765500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>774400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>762600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>743200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>758200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>729600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>711300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>654600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>254600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>249500</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7536,227 +7725,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11700</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
         <v>-73800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>41000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>43400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-43800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>26000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1500</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7794,115 +7992,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>24400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24900</v>
-      </c>
-      <c r="N83" s="3">
-        <v>25200</v>
       </c>
       <c r="O83" s="3">
         <v>25200</v>
       </c>
       <c r="P83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>24500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>23600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>21900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>24800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>23700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>22300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>19700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>14600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8008,8 +8210,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8115,8 +8320,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8222,8 +8430,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8329,8 +8540,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8436,115 +8650,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>27900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>51500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
         <v>41100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>47100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>92200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>97700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>132300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-14600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>86100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>51700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>36300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>83000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>77800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>28300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>21400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8582,115 +8802,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-23900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
         <v>-27800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-24900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8796,8 +9020,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8903,115 +9130,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>-24300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>-27800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-24100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9049,8 +9282,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9078,8 +9312,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9148,16 +9382,19 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9263,8 +9500,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9370,8 +9610,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9477,115 +9720,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-101900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-73700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-122300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-115400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>20800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>150600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9613,8 +9862,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9691,111 +9940,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-98300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>11200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-60400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-133600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>30800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-45700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>80200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>120800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>223800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>55900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>54800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>25400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,488 +656,501 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>486400</v>
+      </c>
+      <c r="E8" s="3">
         <v>510300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>437300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>451500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>451700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>482800</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>438800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>431800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>464800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>468900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>499200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>509600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>527700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>477900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>518000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>549500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>534200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>496700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>485400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>260000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>469700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>401800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>431900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>429500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>461200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>355900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>387400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>385500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>408000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>321800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>346100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>337500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>369900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>277100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E9" s="3">
         <v>205200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>185000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>189900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>193600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>195500</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>183800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>180300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>186100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>222200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>232800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>234600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>236000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>217700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>226500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>235900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>224700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>216500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>210800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>140800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>218600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>187500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>204500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>202500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>212000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>173500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>182600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>177100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>180500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>152400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>162400</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>130300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E10" s="3">
         <v>305100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>252300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>261600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>258200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>287200</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>255000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>251500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>278700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>246700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>266400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>275000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>291700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>260200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>291500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>313600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>309500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>280200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>274600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>119200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>251100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>214300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>227400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>227000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>249200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>182400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>204800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>208400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>227500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>169400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>183700</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>146800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1176,8 +1189,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1286,8 +1300,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1396,126 +1413,132 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>13300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>3100</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>7100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E15" s="3">
         <v>23000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>22700</v>
       </c>
       <c r="F15" s="3">
         <v>22700</v>
@@ -1524,100 +1547,103 @@
         <v>22700</v>
       </c>
       <c r="H15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I15" s="3">
         <v>23200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>22000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24900</v>
-      </c>
-      <c r="O15" s="3">
-        <v>25200</v>
       </c>
       <c r="P15" s="3">
         <v>25200</v>
       </c>
       <c r="Q15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="R15" s="3">
         <v>24500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>25100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>24000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>22200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>21900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>24800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>23700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>22300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>20800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>20400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>20300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>19300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>17600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>17900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>17600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>15400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>14400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>13800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1653,228 +1679,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E17" s="3">
         <v>481600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>440700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>446600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>447600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>454400</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>433800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>425300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>436700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>478700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>483800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>491200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>490400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>469900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>467300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>494700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>472700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>439800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>430600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>301600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>452800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>393400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>430600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>407700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>428800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>377800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>389500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>360600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>369100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>327600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>329500</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>280500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E18" s="3">
         <v>28700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>28300</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>50700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>54800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>61500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>56900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>54800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-41600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>21800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>38900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>16600</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1913,8 +1946,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1945,30 +1979,30 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -2011,460 +2045,475 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
+      <c r="AI20" s="3">
+        <v>0</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E21" s="3">
         <v>51700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>27600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>51600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>50100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>43300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>70700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>69500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>85000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>79500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>32000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>23700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>52800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>17300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>56700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31900</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>10400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4600</v>
+        <v>4200</v>
       </c>
       <c r="E22" s="3">
         <v>4600</v>
       </c>
       <c r="F22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>3700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>3700</v>
       </c>
       <c r="O22" s="3">
         <v>3700</v>
       </c>
       <c r="P22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>700</v>
       </c>
       <c r="S22" s="3">
+        <v>700</v>
+      </c>
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>9400</v>
       </c>
       <c r="AE22" s="3">
         <v>9400</v>
       </c>
       <c r="AF22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>9300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>9700</v>
       </c>
       <c r="AL22" s="3">
         <v>9700</v>
       </c>
+      <c r="AM22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E23" s="3">
         <v>21600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19200</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>45000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>55100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>42300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-57200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>23300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>29500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>25500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>7400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-13400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2573,228 +2622,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E26" s="3">
         <v>14200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11800</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>41000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>43400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>35100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>35300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-43800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>24500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1500</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E27" s="3">
         <v>14200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11700</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>-73800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>41000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>43400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-43800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>24500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1500</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2903,8 +2961,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2912,37 +2973,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>800</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-2100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-73400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>2000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>3300</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2977,8 +3038,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2995,12 +3056,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>42100</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3013,8 +3074,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3123,8 +3187,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3233,8 +3300,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3265,30 +3335,30 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3331,130 +3401,136 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
+      <c r="AI32" s="3">
+        <v>0</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>14200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11700</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>-73800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>43400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-43800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>24500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>26000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1500</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3563,233 +3639,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>14200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11700</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>-73800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>43400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-43800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>24500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>26000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1500</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3828,8 +3913,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3868,118 +3954,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E41" s="3">
         <v>80000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>179500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>150100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>149900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>254600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>246900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>229400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>256200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>254400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>314600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>305800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>439100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>408300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>453800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>373900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>377000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>256300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>263200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>39300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>94100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>82800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>34600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>58400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>27600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24900</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3993,26 +4083,26 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4088,219 +4178,225 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E43" s="3">
         <v>53200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>74300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>87800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>80900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>78900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>80000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79900</v>
-      </c>
-      <c r="N43" s="3">
-        <v>63800</v>
       </c>
       <c r="O43" s="3">
         <v>63800</v>
       </c>
       <c r="P43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="Q43" s="3">
         <v>62200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>55700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>54700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>60000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>44500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>58000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>38900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>45100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>41700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>43200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>39100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>38200</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E44" s="3">
         <v>88600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>93900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>91000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>118600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>119900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>120600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>120900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>123500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>123200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>122000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>129500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>127400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>123700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>124600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>120900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>119500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>111300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>111700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>117900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>130400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>127600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>111900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>105700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>111900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>116000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>99300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>94900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>93700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>89400</v>
       </c>
       <c r="AI44" s="3">
         <v>89400</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>5</v>
+      <c r="AJ44" s="3">
+        <v>89400</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>5</v>
@@ -4308,8 +4404,11 @@
       <c r="AL44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4340,229 +4439,235 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>41400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>22000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>27600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>30800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>24800</v>
       </c>
       <c r="AF45" s="3">
         <v>24800</v>
       </c>
       <c r="AG45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AH45" s="3">
         <v>23900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>22700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>217700</v>
+      </c>
+      <c r="E46" s="3">
         <v>254100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>249800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>243700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>364400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>378900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>396700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>500100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>494300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>486500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>473800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>477100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>480500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>532600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>514600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>646400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>608400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>657000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>566700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>555400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>453100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>441200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>234600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>278600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>270900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>270100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>214700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>211100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>199400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>218600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>162500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>178800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>174400</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>1800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>1800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>900</v>
       </c>
       <c r="K47" s="3">
         <v>900</v>
       </c>
       <c r="L47" s="3">
+        <v>900</v>
+      </c>
+      <c r="M47" s="3">
         <v>1900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4575,8 +4680,8 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4638,228 +4743,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>742400</v>
+      </c>
+      <c r="E48" s="3">
         <v>760400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>770800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>774200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>771500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>768100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>766500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>760800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>765800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>751600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>742600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>738300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>723000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>712300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>701300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>678200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>679200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>679800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>681400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>666200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>681600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>693500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>714900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>716200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>715900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>695300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>355100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>340600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>328000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>311000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>302300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>290700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>281300</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>946800</v>
+      </c>
+      <c r="E49" s="3">
         <v>946900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>947100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>966500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>977500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>977900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>978300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>978900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1049100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1050900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1052800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1054600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1056400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1058300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1060200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1062100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1063900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1065800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1067700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1069500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1071400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1073200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1075100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1077000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1078800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1080600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4968,8 +5082,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5078,118 +5195,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E52" s="3">
         <v>48900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5298,118 +5421,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1968400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2010400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2007800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2020100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2146300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2155400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2172500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2266400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2333900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2312400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2291200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2291700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2278300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2325500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2293100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2405500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2369200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2419800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2333500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2307500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2219000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2218700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2032700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2078400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2071800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2053100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5448,8 +5577,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5488,219 +5618,223 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E57" s="3">
         <v>36700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>53600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>67600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>74600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>65300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>70000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>69400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>64300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>76100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>77700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>79800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>64900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>68600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>52400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>60000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>45300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>47100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>45100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>43600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>30900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>46100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>35700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>33600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>34400</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E58" s="3">
         <v>202200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>201100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>189900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>399900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>96600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>95600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>93100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>82300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>75300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>4700</v>
       </c>
       <c r="P58" s="3">
         <v>4700</v>
       </c>
       <c r="Q58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R58" s="3">
         <v>4000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13700</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>8500</v>
       </c>
       <c r="AB58" s="3">
         <v>8500</v>
       </c>
       <c r="AC58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AD58" s="3">
         <v>7600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>7300</v>
       </c>
       <c r="AG58" s="3">
         <v>7300</v>
       </c>
       <c r="AH58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AI58" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>5</v>
+      <c r="AJ58" s="3">
+        <v>9600</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>5</v>
@@ -5708,448 +5842,463 @@
       <c r="AL58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>234200</v>
+      </c>
+      <c r="E59" s="3">
         <v>227900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>150200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>146400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>150500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>150900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>147600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>148500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>163000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>274900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>263700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>279100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>271300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>275500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>268300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>288500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>275900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>260200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>283900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>256200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>224000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>218600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>244800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>232700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>244100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>160400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>158500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>148800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>168200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>169500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>176000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>167900</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>418200</v>
+      </c>
+      <c r="E60" s="3">
         <v>468200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>468300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>426100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>663200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>375000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>397700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>373500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>363200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>361800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>344300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>336600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>353800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>345400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>343800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>348800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>370500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>359800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>328700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>356000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>311900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>287500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>273200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>303900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>288300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>297700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>211700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>197200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>189300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>221700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>211300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>219200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>211900</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600300</v>
+      </c>
+      <c r="E61" s="3">
         <v>602900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>614900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>641500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>526500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>828700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>827600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>927000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>935900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>935400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>563400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>564200</v>
       </c>
       <c r="O61" s="3">
         <v>564200</v>
       </c>
       <c r="P61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="Q61" s="3">
         <v>564700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>566100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>615600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>616200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>733700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>651800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>648100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>644900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>713200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>555900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>584300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>579100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>578400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>570500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>566900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>562000</v>
       </c>
       <c r="AG61" s="3">
         <v>562000</v>
       </c>
       <c r="AH61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>912700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>913300</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E62" s="3">
         <v>8400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>8400</v>
       </c>
       <c r="H62" s="3">
         <v>8400</v>
       </c>
       <c r="I62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>482500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>484000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>468700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>464700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>457200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>452500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>444200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>438800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>446600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>438400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>441200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>431900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>427200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>424800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>430000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>414400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>136000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>138400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>154000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>149600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>154100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>202400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>202000</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6258,8 +6407,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6368,8 +6520,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6478,118 +6633,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1117800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1174200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1191400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1180100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1302900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1314000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1343100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1426100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1425500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1415600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1390100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1384800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1386700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1374800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1367100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1416900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1430900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1532300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1427000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1442600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1398100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1432600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1256300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1313000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1297400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1290500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>918200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>902500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>909900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>933300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>927300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6628,8 +6789,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6738,8 +6900,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6848,8 +7013,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6958,8 +7126,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7068,118 +7239,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E72" s="3">
         <v>240300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>226100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>254700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>263200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>266300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>254600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>270600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>344400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>338800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>320500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>329800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>318300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>308500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>278400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>272200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>231200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>193600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>142900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>107800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>72500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>116300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>107100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>103200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>102000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>91800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>74800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>100100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>94300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>81200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7288,8 +7465,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7398,8 +7578,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7508,118 +7691,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>850600</v>
+      </c>
+      <c r="E76" s="3">
         <v>836200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>816300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>840000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>843400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>841300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>829400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>840400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>908400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>896700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>901100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>906900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>891700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>950700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>926000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>988600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>938300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>887500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>906500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>865000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>820900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>786200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>776400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>765500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>774400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>762600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>743200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>758200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>729600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>711300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>654600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>254600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>249500</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7728,233 +7917,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>14200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11700</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>-73800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>43400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-43800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>24500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>26000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1500</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7993,118 +8191,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3">
         <v>23800</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3">
+        <v>24400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="K83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="L83" s="3">
         <v>23400</v>
       </c>
-      <c r="H83" s="3">
-        <v>24400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>22800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>23000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>23400</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24900</v>
-      </c>
-      <c r="O83" s="3">
-        <v>25200</v>
       </c>
       <c r="P83" s="3">
         <v>25200</v>
       </c>
       <c r="Q83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="R83" s="3">
         <v>24500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>23600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>23700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>22300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>15200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>19700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>14400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>13800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8213,8 +8415,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8323,8 +8528,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8433,8 +8641,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8543,8 +8754,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8653,118 +8867,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E89" s="3">
         <v>32200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3">
         <v>27900</v>
       </c>
-      <c r="G89" s="3">
-        <v>51500</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3">
         <v>24000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>41100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>74100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>47100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>92200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>97700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>132300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-14600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>86100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>51700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>36300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>83000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>77800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>28300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>46500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8803,118 +9023,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20200</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3">
         <v>-23900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-19600</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-27800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-24900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9023,8 +9247,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9133,118 +9360,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20200</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3">
         <v>-24300</v>
       </c>
-      <c r="G94" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3">
         <v>-18200</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-27800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9283,8 +9516,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9315,8 +9549,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9385,16 +9619,19 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9503,8 +9740,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9613,8 +9853,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9723,118 +9966,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5400</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3">
         <v>-101900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3">
         <v>-5200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-73700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-122300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-115400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>20800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>150600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9865,8 +10114,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9943,114 +10192,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E102" s="3">
         <v>6600</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-98300</v>
       </c>
-      <c r="G102" s="3">
-        <v>29400</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>11200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-60400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-133600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-45700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>80200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>120800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>223800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>55900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>54800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>25400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,514 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>503400</v>
+      </c>
+      <c r="E8" s="3">
         <v>487300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>486400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>510300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>437300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>451500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>451700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>482800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>438800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>431800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>464800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>468900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>499200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>509600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>527700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>477900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>518000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>549500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>534200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>496700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>485400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>260000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>469700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>401800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>431900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>429500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>461200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>355900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>387400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>385500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>408000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>321800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>346100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>337500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>369900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>277100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>210700</v>
+      </c>
+      <c r="E9" s="3">
         <v>203200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>205200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>185000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>189900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>193600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>195500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>183800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>180300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>222200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>232800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>234600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>236000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>217700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>226500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>235900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>224700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>216500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>210800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>140800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>218600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>187500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>204500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>202500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>212000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>173500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>182600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>177100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>180500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>152400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>162400</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="3">
         <v>130300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E10" s="3">
         <v>284100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>286100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>305100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>252300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>261600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>258200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>287200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>255000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>251500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>278700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>246700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>266400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>275000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>291700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>260200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>291500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>313600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>309500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>280200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>274600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>119200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>251100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>214300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>227400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>227000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>249200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>182400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>204800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>208400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>227500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>169400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>183700</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="3">
         <v>146800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1204,8 +1217,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1320,8 +1334,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1436,138 +1453,144 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>2700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
-        <v>22200</v>
-      </c>
       <c r="H14" s="3">
+        <v>22300</v>
+      </c>
+      <c r="I14" s="3">
         <v>12900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>13300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>8000</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>7100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E15" s="3">
         <v>22200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>22700</v>
       </c>
       <c r="H15" s="3">
         <v>22700</v>
@@ -1576,100 +1599,103 @@
         <v>22700</v>
       </c>
       <c r="J15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="K15" s="3">
         <v>23200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>22500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24900</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>25200</v>
       </c>
       <c r="R15" s="3">
         <v>25200</v>
       </c>
       <c r="S15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="T15" s="3">
         <v>24500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>25100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>24000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>23600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>22600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>22200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>21900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>24800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>23700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>22300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>20800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>20400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>20300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>19300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>17600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>17900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>15400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>14600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>14400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>13800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1707,240 +1733,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>494600</v>
+      </c>
+      <c r="E17" s="3">
         <v>475000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>470000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>481600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>440600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>446600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>447600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>454400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>433800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>425300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>436700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>478700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>483800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>491200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>490400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>469900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>467300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>494700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>472700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>439800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>430600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>301600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>452800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>393400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>430600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>407700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>428800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>377800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>389500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>360600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>369100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>327600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>329500</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
         <v>280500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E18" s="3">
         <v>12300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>28300</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>28200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>15400</v>
+      </c>
+      <c r="R18" s="3">
+        <v>18400</v>
+      </c>
+      <c r="S18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="T18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>50700</v>
+      </c>
+      <c r="V18" s="3">
+        <v>54800</v>
+      </c>
+      <c r="W18" s="3">
+        <v>61500</v>
+      </c>
+      <c r="X18" s="3">
+        <v>56900</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>54800</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>8400</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>21800</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>32400</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>24900</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>38900</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>16600</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="3">
         <v>-3400</v>
       </c>
-      <c r="H18" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>28300</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
-        <v>5000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>6500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>28200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="P18" s="3">
-        <v>15400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>18400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>37300</v>
-      </c>
-      <c r="S18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>50700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>54800</v>
-      </c>
-      <c r="V18" s="3">
-        <v>61500</v>
-      </c>
-      <c r="W18" s="3">
-        <v>56900</v>
-      </c>
-      <c r="X18" s="3">
-        <v>54800</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-41600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>16900</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>21800</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>32400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>24900</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>38900</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>16600</v>
-      </c>
-      <c r="AK18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1981,8 +2014,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2019,30 +2053,30 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -2085,484 +2119,499 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>5</v>
+      <c r="AK20" s="3">
+        <v>0</v>
       </c>
       <c r="AL20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
+      <c r="AM20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E21" s="3">
         <v>34500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>28500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>50100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>43300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>70300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>70700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>69500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>85000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>79500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>32000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>52800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>17300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>42600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>56700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>31900</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>10400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E22" s="3">
         <v>4100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4600</v>
       </c>
       <c r="G22" s="3">
         <v>4600</v>
       </c>
       <c r="H22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>3700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>3700</v>
       </c>
       <c r="Q22" s="3">
         <v>3700</v>
       </c>
       <c r="R22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S22" s="3">
         <v>3600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>700</v>
       </c>
       <c r="T22" s="3">
         <v>700</v>
       </c>
       <c r="U22" s="3">
+        <v>700</v>
+      </c>
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>9400</v>
       </c>
       <c r="AG22" s="3">
         <v>9400</v>
       </c>
       <c r="AH22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>9300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>16400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>14900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>14600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>9700</v>
       </c>
       <c r="AN22" s="3">
         <v>9700</v>
       </c>
+      <c r="AO22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>41500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>45000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>55100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>29500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>25500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>8500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2677,240 +2726,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>41000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>43400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>35100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>24500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1500</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>-73800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>41000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>43400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>24500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1500</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3025,8 +3083,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3040,37 +3101,37 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>800</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-73400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>2000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>3300</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3105,8 +3166,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3123,12 +3184,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>42100</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3141,8 +3202,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3257,8 +3321,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3373,8 +3440,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3411,30 +3481,30 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3477,136 +3547,142 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>5</v>
+      <c r="AK32" s="3">
+        <v>0</v>
       </c>
       <c r="AL32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
+      <c r="AM32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>-73800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>41000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>43400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>24500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1500</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3721,245 +3797,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>-73800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>41000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>43400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>24500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1500</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4000,8 +4085,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4042,124 +4128,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E41" s="3">
         <v>56000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>81200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>179500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>150100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>265800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>254600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>246900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>229400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>256200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>254400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>314600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>305800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>439100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>408300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>453800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>373900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>377000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>256300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>263200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>39300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>94100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>82800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>72500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>17100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>48900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>34600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>58400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>27600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24900</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4179,26 +4269,26 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9300</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4274,231 +4364,237 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E43" s="3">
         <v>46100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>74300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>87800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>80900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>78900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>80000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>63800</v>
       </c>
       <c r="Q43" s="3">
         <v>63800</v>
       </c>
       <c r="R43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="S43" s="3">
         <v>62200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>55700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>54100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>60000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>44500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>58000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>50700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>38900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>45100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>41700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>39100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>38200</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E44" s="3">
         <v>88000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>89600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>88600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>93900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>87600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>91000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>118600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>119900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>120600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>123500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>123200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>122000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>129500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>127400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>123700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>124600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>120900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>119500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>111300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>111700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>117900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>130400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>127600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>111900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>105700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>111900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>116000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>99300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>94900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>93700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AJ44" s="3">
-        <v>89400</v>
       </c>
       <c r="AK44" s="3">
         <v>89400</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>5</v>
+      <c r="AL44" s="3">
+        <v>89400</v>
       </c>
       <c r="AM44" s="3" t="s">
         <v>5</v>
@@ -4506,8 +4602,11 @@
       <c r="AN44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4544,241 +4643,247 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>41400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>23300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>25000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>27600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>30800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>24800</v>
       </c>
       <c r="AH45" s="3">
         <v>24800</v>
       </c>
       <c r="AI45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>22700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>22000</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E46" s="3">
         <v>220200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>217700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>254100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>243700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>364400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>378900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>396700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>500100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>494300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>486500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>473800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>477100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>480500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>532600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>514600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>646400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>608400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>657000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>566700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>555400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>453100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>441200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>234600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>278600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>270900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>270100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>214700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>211100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>199400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>218600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>162500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>178800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>174400</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3300</v>
+        <v>4000</v>
       </c>
       <c r="E47" s="3">
         <v>3300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>1800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3300</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>1800</v>
-      </c>
-      <c r="L47" s="3">
-        <v>900</v>
       </c>
       <c r="M47" s="3">
         <v>900</v>
       </c>
       <c r="N47" s="3">
+        <v>900</v>
+      </c>
+      <c r="O47" s="3">
         <v>1900</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4791,8 +4896,8 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4854,240 +4959,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>739500</v>
+      </c>
+      <c r="E48" s="3">
         <v>726900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>742400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>760400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>770800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>774200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>771500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>768100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>766500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>760800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>765800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>751600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>742600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>738300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>723000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>712300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>701300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>678200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>679200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>679800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>681400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>666200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>681600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>693500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>714900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>716200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>715900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>695300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>355100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>340600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>328000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>311000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>302300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>290700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>281300</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>948700</v>
+      </c>
+      <c r="E49" s="3">
         <v>948900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>946800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>946900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>947100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>966500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>977500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>977900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>978300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>978900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1049100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1050900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1052800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1054600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1056400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1058300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1060200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1062100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1063900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1065800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1067700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1069500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1071400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1073200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1075100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1077000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1078800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1080600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5202,8 +5316,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5318,124 +5435,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E52" s="3">
         <v>59100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>58200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10500</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5550,124 +5673,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1983700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1958500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1968400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2010400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2007800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2020100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2146300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2155400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2172500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2266400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2333900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2312400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2291200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2291700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2278300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2325500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2293100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2405500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2369200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2419800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2333500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2307500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2219000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2218700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2032700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2078400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2071800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2053100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5708,8 +5837,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5750,231 +5880,235 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E57" s="3">
         <v>74300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>53600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>39600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>50000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>60800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>64100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>74600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>65300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>69000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>70000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>64300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>76100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>77700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>79800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>64900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>68600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>52400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>60000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>45300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>47100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>45100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>43600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>32800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>46100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>35700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>33600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>34400</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E58" s="3">
         <v>119200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>119000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>202200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>201100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>189900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>399900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>96600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>95600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>93100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>82300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>4700</v>
       </c>
       <c r="R58" s="3">
         <v>4700</v>
       </c>
       <c r="S58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T58" s="3">
         <v>4000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13700</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>8500</v>
       </c>
       <c r="AD58" s="3">
         <v>8500</v>
       </c>
       <c r="AE58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AF58" s="3">
         <v>7600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>7300</v>
       </c>
       <c r="AI58" s="3">
         <v>7300</v>
       </c>
       <c r="AJ58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AK58" s="3">
         <v>9600</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>5</v>
+      <c r="AL58" s="3">
+        <v>9600</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>5</v>
@@ -5982,472 +6116,487 @@
       <c r="AN58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>158400</v>
+      </c>
+      <c r="E59" s="3">
         <v>223500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>234200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>227900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>150200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>146400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>150500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>165600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>150900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>147600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>148500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>274900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>263700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>279100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>271300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>275500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>268300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>288500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>275900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>260200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>283900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>256200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>224000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>218600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>244800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>232700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>244100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>160400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>158500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>148800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>168200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>169500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>176000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>167900</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>412400</v>
+      </c>
+      <c r="E60" s="3">
         <v>417000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>418200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>468200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>468300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>426100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>663200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>375000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>397700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>373500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>363200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>361800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>344300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>336600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>353800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>345400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>343800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>348800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>370500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>359800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>328700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>356000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>311900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>287500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>273200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>303900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>288300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>297700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>197200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>189300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>221700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>211300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>219200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>211900</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E61" s="3">
         <v>574300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>600300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>602900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>614900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>641500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>526500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>828700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>827600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>927000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>935900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>935400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>563400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>564200</v>
       </c>
       <c r="Q61" s="3">
         <v>564200</v>
       </c>
       <c r="R61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="S61" s="3">
         <v>564700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>566100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>615600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>616200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>733700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>651800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>648100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>644900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>713200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>555900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>584300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>579100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>578400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>570500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>566900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>562000</v>
       </c>
       <c r="AI61" s="3">
         <v>562000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>912700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>913300</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E62" s="3">
         <v>8400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>8400</v>
       </c>
       <c r="J62" s="3">
         <v>8400</v>
       </c>
       <c r="K62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>482500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>484000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>468700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>464700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>457200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>452500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>444200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>438800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>446600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>438400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>441200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>431900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>427200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>424800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>430000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>414400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>136000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>138400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>154000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>149600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>154100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>202400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>202000</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6562,8 +6711,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6678,8 +6830,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6794,124 +6949,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1114100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1099700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1117800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1174200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1191400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1180100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1302900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1314000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1343100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1426100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1425500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1415600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1390100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1384800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1386700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1374800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1367100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1416900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1430900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1532300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1427000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1442600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1398100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1432600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1256300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1313000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1297400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1290500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>918200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>902500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>909900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>933300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>927300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6952,8 +7113,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7068,8 +7230,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7184,8 +7349,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7300,8 +7468,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7416,124 +7587,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>255700</v>
+      </c>
+      <c r="E72" s="3">
         <v>252400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>249000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>240300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>226100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>254700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>263200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>266300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>254600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>270600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>344400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>338800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>320500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>329800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>318300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>308500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>278400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>272200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>231200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>193600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>142900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>107800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>72500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>116300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>107100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>103200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>102000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>91800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>74800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>100100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>94300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>81200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6900</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7648,8 +7825,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7764,8 +7944,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7880,124 +8063,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>869500</v>
+      </c>
+      <c r="E76" s="3">
         <v>858800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>850600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>836200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>816300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>840000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>843400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>841300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>829400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>840400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>908400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>896700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>901100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>906900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>891700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>950700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>926000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>988600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>938300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>887500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>906500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>865000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>820900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>786200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>776400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>765500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>774400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>762600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>743200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>758200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>729600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>711300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>654600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>254600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>249500</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8112,245 +8301,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>-73800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>41000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>43400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>24500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1500</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8391,124 +8589,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E83" s="3">
         <v>22300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3">
         <v>23800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24400</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>24400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24900</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>25200</v>
       </c>
       <c r="R83" s="3">
         <v>25200</v>
       </c>
       <c r="S83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="T83" s="3">
         <v>24500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>23600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>22600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>24800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>23700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>15200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>19700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>21700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>14600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>14400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>13800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8623,8 +8825,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8739,8 +8944,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8855,8 +9063,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8971,8 +9182,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9087,124 +9301,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E89" s="3">
         <v>46600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>54300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27900</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>24000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>41100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>74100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>40900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>47100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>25100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>44000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>92200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>97700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>31300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>132300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>86100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>51700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>36300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>83000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>77800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>28300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>21400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>46500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>6500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9245,124 +9465,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-27800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9477,8 +9701,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9593,124 +9820,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24300</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-18200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-27800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-36500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9751,8 +9984,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9789,8 +10023,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9859,16 +10093,19 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9983,8 +10220,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10099,8 +10339,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10215,124 +10458,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-73400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-101900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>-5200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-73700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-122300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-115400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>20800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>150600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10369,8 +10618,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10447,120 +10696,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E102" s="3">
         <v>7600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-98300</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>11200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-133600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>30800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-45700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>80200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>120800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>223800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>10000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>55900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>54800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>25400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>EYE</t>
   </si>
@@ -656,527 +656,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="2">
         <v>46025</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44562</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44198</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>543900</v>
+      </c>
+      <c r="E8" s="3">
         <v>503400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>487300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>486400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>510300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>437300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>451500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>451700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>482800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <v>438800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>431800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>464800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>468900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>499200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>509600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>527700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>477900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>518000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>549500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>534200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>496700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>485400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>260000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>469700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>401800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>431900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>429500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>461200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>355900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>387400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>385500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>408000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>321800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>346100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>337500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>369900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>277100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>219100</v>
+      </c>
+      <c r="E9" s="3">
         <v>210700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>203200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>205200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>185000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>189900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>193600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>195500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>183800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>180300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>222200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>232800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>234600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>236000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>217700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>226500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>235900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>224700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>216500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>210800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>140800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>218600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>187500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>204500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>202500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>212000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>173500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>182600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>177100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>180500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>152400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>162400</v>
       </c>
-      <c r="AL9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3">
         <v>130300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>324700</v>
+      </c>
+      <c r="E10" s="3">
         <v>292700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>284100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>286100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>305100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>252300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>261600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>258200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>287200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>255000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>251500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>278700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>246700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>266400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>275000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>291700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>260200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>291500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>313600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>309500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>280200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>274600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>119200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>251100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>214300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>227400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>227000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>249200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>182400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>204800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>208400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>227500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>169400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>183700</v>
       </c>
-      <c r="AL10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3">
         <v>146800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1218,8 +1230,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1337,8 +1350,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1456,144 +1472,150 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2100</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>3100</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>8000</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>7100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E15" s="3">
         <v>23500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>22700</v>
       </c>
       <c r="I15" s="3">
         <v>22700</v>
@@ -1602,100 +1624,103 @@
         <v>22700</v>
       </c>
       <c r="K15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="L15" s="3">
         <v>23200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>24900</v>
-      </c>
-      <c r="R15" s="3">
-        <v>25200</v>
       </c>
       <c r="S15" s="3">
         <v>25200</v>
       </c>
       <c r="T15" s="3">
+        <v>25200</v>
+      </c>
+      <c r="U15" s="3">
         <v>24500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>25100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>24000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>23600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>22600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>22200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>21900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>24800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>23700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>22300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>20800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>20400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>20300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>19300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>17600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>17600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>15400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>14600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>14400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>13800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1734,246 +1759,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E17" s="3">
         <v>494600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>475000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>470000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>481600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>440600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>446600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>447600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>454400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>433800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>425300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>436700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>478700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>483800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>491200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>490400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>469900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>467300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>494700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>472700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>439800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>430600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>301600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>452800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>393400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>430600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>407700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>428800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>377800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>389500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>360600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>369100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>327600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>329500</v>
       </c>
-      <c r="AL17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AN17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="3">
         <v>280500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>286900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E18" s="3">
         <v>8800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>28700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>5000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>50700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>54800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>61500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>56900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>54800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-41600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>21800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>38900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>16600</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2015,8 +2047,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2056,30 +2089,30 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -2122,496 +2155,511 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>5</v>
+      <c r="AL20" s="3">
+        <v>0</v>
       </c>
       <c r="AM20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN20" s="3">
-        <v>0</v>
+      <c r="AN20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E21" s="3">
         <v>32300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>34500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>50100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>43300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>70300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>70700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>69500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>85000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>79500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>77000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>41700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>32000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>52800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>17300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>42600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>56700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>11800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>31900</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="3">
         <v>10400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>4600</v>
       </c>
       <c r="H22" s="3">
         <v>4600</v>
       </c>
       <c r="I22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>3700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>3700</v>
       </c>
       <c r="R22" s="3">
         <v>3700</v>
       </c>
       <c r="S22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T22" s="3">
         <v>3600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>700</v>
       </c>
       <c r="U22" s="3">
         <v>700</v>
       </c>
       <c r="V22" s="3">
+        <v>700</v>
+      </c>
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>9400</v>
       </c>
       <c r="AH22" s="3">
         <v>9400</v>
       </c>
       <c r="AI22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>16400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>14900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>14600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>14200</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>9700</v>
       </c>
       <c r="AO22" s="3">
         <v>9700</v>
       </c>
+      <c r="AP22" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>41500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>45000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>55100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>42300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>23300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>29500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-22200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>25500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>8500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2729,246 +2777,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>41000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>37600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>43400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>35300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1500</v>
       </c>
-      <c r="AL26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AN26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>-73800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>41000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>43400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1500</v>
       </c>
-      <c r="AL27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AN27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3086,8 +3143,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3104,37 +3164,37 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>800</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-2100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-73400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>2000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>3300</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3169,8 +3229,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3187,12 +3247,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>42100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3205,8 +3265,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3324,8 +3387,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3443,8 +3509,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3484,30 +3553,30 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3550,139 +3619,145 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>5</v>
+      <c r="AL32" s="3">
+        <v>0</v>
       </c>
       <c r="AM32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN32" s="3">
-        <v>0</v>
+      <c r="AN32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>-73800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>43400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>26000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1500</v>
       </c>
-      <c r="AL33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AN33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3800,251 +3875,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>-73800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>43400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>26000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1500</v>
       </c>
-      <c r="AL35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AN35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E38" s="2">
         <v>46025</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44562</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44198</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4086,8 +4170,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4129,132 +4214,136 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E41" s="3">
         <v>38700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>73900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>81200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>179500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>150100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>265800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>254600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>246900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>229400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>256200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>254400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>314600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>305800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>439100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>408300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>453800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>373900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>377000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>256300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>263200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>39300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>94100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>82800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>72500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>48900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>34600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>58400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>27600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24900</v>
       </c>
-      <c r="AM41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4272,26 +4361,26 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4367,237 +4456,243 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E43" s="3">
         <v>58300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>61100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>74300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>87800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>80900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>78900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>80000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>79900</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>63800</v>
       </c>
       <c r="R43" s="3">
         <v>63800</v>
       </c>
       <c r="S43" s="3">
+        <v>63800</v>
+      </c>
+      <c r="T43" s="3">
         <v>62200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>55700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>60000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>58500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>44500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>58000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>50700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>38900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>45100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>43200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>39100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>38200</v>
       </c>
-      <c r="AM43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO43" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP43" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E44" s="3">
         <v>89300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>88000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>89600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>88600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>93900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>87600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>91000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>118600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>119900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>120900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>123500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>123200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>122000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>129500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>127400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>123700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>124600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>120900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>119500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>111300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>111700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>117900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>130400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>127600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>111900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>105700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>111900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>116000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>99300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>94900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>93700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>91200</v>
-      </c>
-      <c r="AK44" s="3">
-        <v>89400</v>
       </c>
       <c r="AL44" s="3">
         <v>89400</v>
       </c>
-      <c r="AM44" s="3" t="s">
-        <v>5</v>
+      <c r="AM44" s="3">
+        <v>89400</v>
       </c>
       <c r="AN44" s="3" t="s">
         <v>5</v>
@@ -4605,8 +4700,11 @@
       <c r="AO44" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP44" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4646,247 +4744,253 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>41400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>28600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>17100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>23300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>27600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>30800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24100</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>24800</v>
       </c>
       <c r="AI45" s="3">
         <v>24800</v>
       </c>
       <c r="AJ45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="AK45" s="3">
         <v>23900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>22700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>22000</v>
       </c>
-      <c r="AM45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E46" s="3">
         <v>225700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>220200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>217700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>254100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>249800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>243700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>364400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>378900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>396700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>500100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>494300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>486500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>473800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>477100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>480500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>532600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>514600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>646400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>608400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>657000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>566700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>555400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>453100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>441200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>234600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>278600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>270900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>270100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>214700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>211100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>199400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>218600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>162500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>178800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>174400</v>
       </c>
-      <c r="AM46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO46" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP46" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E47" s="3">
         <v>4000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3300</v>
       </c>
       <c r="F47" s="3">
         <v>3300</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>1800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3300</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>1800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>900</v>
       </c>
       <c r="N47" s="3">
         <v>900</v>
       </c>
       <c r="O47" s="3">
+        <v>900</v>
+      </c>
+      <c r="P47" s="3">
         <v>1900</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4899,8 +5003,8 @@
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4962,8 +5066,11 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4971,237 +5078,243 @@
         <v>739500</v>
       </c>
       <c r="E48" s="3">
+        <v>739500</v>
+      </c>
+      <c r="F48" s="3">
         <v>726900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>742400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>760400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>770800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>774200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>771500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>768100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>766500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>760800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>765800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>751600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>742600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>738300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>723000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>712300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>701300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>678200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>679200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>679800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>681400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>666200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>681600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>693500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>714900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>716200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>715900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>695300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>355100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>340600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>328000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>311000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>302300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>290700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>281300</v>
       </c>
-      <c r="AM48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>948900</v>
+      </c>
+      <c r="E49" s="3">
         <v>948700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>948900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>946800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>946900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>947100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>966500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>977500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>977900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>978300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>978900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1049100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1050900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1052800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1054600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1056400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1058300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1060200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1062100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1063900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1065800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1067700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1069500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1071400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1073200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1075100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1077000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1078800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1080600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1082700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1099900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1102000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1104100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1106200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1108300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1110400</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5319,8 +5432,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5438,8 +5554,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5447,118 +5566,121 @@
         <v>65700</v>
       </c>
       <c r="E52" s="3">
+        <v>65700</v>
+      </c>
+      <c r="F52" s="3">
         <v>59100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>48900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>11100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10500</v>
       </c>
-      <c r="AM52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5676,127 +5798,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2020500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1983700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1958500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1968400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2010400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2007800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2020100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2146300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2155400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2172500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2266400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2333900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2312400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2291200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2291700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2278300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2325500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2293100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2405500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2369200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2419800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2333500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2307500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2219000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2218700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2032700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2078400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2071800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2053100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1661400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1660700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1639400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1644600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1581900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1588900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1576700</v>
       </c>
-      <c r="AM54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5838,8 +5966,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5881,237 +6010,241 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E57" s="3">
         <v>79000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>65100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>50000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>60800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>64100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>74600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>65300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>69000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>70000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>64300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>76100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>77700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>79800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>64900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>68600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>52400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>60000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>45300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>47100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>45100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>43600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>30900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>32800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>35700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>33600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>34400</v>
       </c>
-      <c r="AM57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E58" s="3">
         <v>106900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>119200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>119000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>202200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>201100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>189900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>399900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>96600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>95600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>93100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>82300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>75300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>4700</v>
       </c>
       <c r="S58" s="3">
         <v>4700</v>
       </c>
       <c r="T58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U58" s="3">
         <v>4000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>13700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>8500</v>
       </c>
       <c r="AE58" s="3">
         <v>8500</v>
       </c>
       <c r="AF58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AG58" s="3">
         <v>7600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7700</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>7300</v>
       </c>
       <c r="AJ58" s="3">
         <v>7300</v>
       </c>
       <c r="AK58" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="AL58" s="3">
         <v>9600</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>5</v>
+      <c r="AM58" s="3">
+        <v>9600</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>5</v>
@@ -6119,484 +6252,499 @@
       <c r="AO58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E59" s="3">
         <v>158400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>223500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>234200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>227900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>150200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>146400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>150500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>165600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>150900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>147600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>148500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>163000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>274900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>263700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>279100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>271300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>275500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>268300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>288500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>275900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>260200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>283900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>256200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>224000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>218600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>244800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>232700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>244100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>160400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>158500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>148800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>168200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>169500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>176000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>167900</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>418500</v>
+      </c>
+      <c r="E60" s="3">
         <v>412400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>417000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>418200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>468200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>468300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>426100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>663200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>375000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>397700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>373500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>363200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>361800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>344300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>336600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>353800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>345400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>343800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>348800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>370500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>359800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>328700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>356000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>311900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>287500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>273200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>303900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>288300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>297700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>211700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>197200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>189300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>221700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>211300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>219200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>211900</v>
       </c>
-      <c r="AM60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO60" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>584200</v>
+      </c>
+      <c r="E61" s="3">
         <v>587700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>574300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>602900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>614900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>641500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>526500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>828700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>827600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>927000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>935900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>935400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>563400</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>564200</v>
       </c>
       <c r="R61" s="3">
         <v>564200</v>
       </c>
       <c r="S61" s="3">
+        <v>564200</v>
+      </c>
+      <c r="T61" s="3">
         <v>564700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>566100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>615600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>616200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>733700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>651800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>648100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>644900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>713200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>555900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>584300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>579100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>578400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>570500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>566900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>566600</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>562000</v>
       </c>
       <c r="AJ61" s="3">
         <v>562000</v>
       </c>
       <c r="AK61" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AL61" s="3">
         <v>912700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>913300</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>8400</v>
       </c>
       <c r="K62" s="3">
         <v>8400</v>
       </c>
       <c r="L62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="M62" s="3">
         <v>8500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>482500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>484000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>468700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>464700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>457200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>452500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>444200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>438800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>446600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>438400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>441200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>431900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>427200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>424800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>430000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>414400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>136000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>138400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>154000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>149600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>154100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>202400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>202000</v>
       </c>
-      <c r="AM62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6714,8 +6862,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6833,8 +6984,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6952,127 +7106,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1122500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1114100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1099700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1117800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1174200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1191400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1180100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1302900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1314000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1343100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1426100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1425500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1415600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1390100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1384800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1386700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1374800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1367100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1416900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1430900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1532300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1427000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1442600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1398100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1432600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1256300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1313000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1297400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1290500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>918200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>902500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>909900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>933300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>927300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1334300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1327200</v>
       </c>
-      <c r="AM66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7114,8 +7274,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7233,8 +7394,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7352,8 +7516,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7471,8 +7638,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7590,127 +7760,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>286900</v>
+      </c>
+      <c r="E72" s="3">
         <v>255700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>252400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>249000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>240300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>226100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>254700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>263200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>266300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>254600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>270600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>344400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>338800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>320500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>329800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>318300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>308500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>278400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>272200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>231200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>193600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>142900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>107800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>72500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>116300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>107100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>103200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>102000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>91800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>74800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>100100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>94300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>81200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>32200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6900</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7828,8 +8004,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7947,8 +8126,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8066,127 +8248,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E76" s="3">
         <v>869500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>858800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>850600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>836200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>816300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>840000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>843400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>841300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>829400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>840400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>908400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>896700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>901100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>906900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>891700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>950700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>926000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>988600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>938300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>887500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>906500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>865000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>820900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>786200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>776400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>765500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>774400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>762600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>743200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>758200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>729600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>711300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>654600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>254600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>249500</v>
       </c>
-      <c r="AM76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AO76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8304,251 +8492,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="2">
         <v>46025</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44562</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44198</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>-73800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>43400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>26000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1500</v>
       </c>
-      <c r="AL81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AN81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8590,127 +8787,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E83" s="3">
         <v>22600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
         <v>23800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24400</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>24400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>22800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>25200</v>
       </c>
       <c r="S83" s="3">
         <v>25200</v>
       </c>
       <c r="T83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="U83" s="3">
         <v>24500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>23600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>22200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>24800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>19600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>15200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>21700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>14600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>14400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>13800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8828,8 +9029,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8947,8 +9151,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9066,8 +9273,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9185,8 +9395,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9304,127 +9517,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E89" s="3">
         <v>13200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>54300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27900</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>24000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>41100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>74100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>40900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>47100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>44000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>92200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>97700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>31300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>132300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>86100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>51700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>83000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>77800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>28300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>21400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>46500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>6500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9466,127 +9685,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-27800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-30400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-20200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9704,8 +9927,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9823,127 +10049,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-27800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-28100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-36500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-23400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-21000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9985,8 +10217,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10026,8 +10259,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10096,16 +10329,19 @@
         <v>0</v>
       </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-171000</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10223,8 +10459,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10342,8 +10581,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10461,127 +10703,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-73400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-101900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-5200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-73700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-122300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-115400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>20800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>150600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10621,8 +10869,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10699,123 +10947,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-31900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-98300</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-60400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-133600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-45700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>80200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>120800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>223800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>55900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-32100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>54800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-23400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>25400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>4100</v>
       </c>
     </row>
